--- a/state/01078_challex.xlsx
+++ b/state/01078_challex.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,7 +25,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
@@ -34,18 +33,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Display"/>
+      <name val="Cambria"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="53">
@@ -391,26 +396,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -429,16 +414,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -685,17 +686,21 @@
     <xf numFmtId="0" fontId="2" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -780,7 +785,7 @@
     </from>
     <to>
       <col>34</col>
-      <colOff>761952</colOff>
+      <colOff>609552</colOff>
       <row>1</row>
       <rowOff>423843</rowOff>
     </to>
@@ -820,8 +825,8 @@
       <rowOff>71462</rowOff>
     </from>
     <to>
-      <col>36</col>
-      <colOff>709613</colOff>
+      <col>37</col>
+      <colOff>953</colOff>
       <row>1</row>
       <rowOff>461938</rowOff>
     </to>
@@ -861,8 +866,8 @@
       <rowOff>123843</rowOff>
     </from>
     <to>
-      <col>39</col>
-      <colOff>628619</colOff>
+      <col>40</col>
+      <colOff>3779</colOff>
       <row>1</row>
       <rowOff>409557</rowOff>
     </to>
@@ -903,7 +908,7 @@
     </from>
     <to>
       <col>64</col>
-      <colOff>742950</colOff>
+      <colOff>605790</colOff>
       <row>1</row>
       <rowOff>452415</rowOff>
     </to>
@@ -943,8 +948,8 @@
       <rowOff>128605</rowOff>
     </from>
     <to>
-      <col>60</col>
-      <colOff>719096</colOff>
+      <col>61</col>
+      <colOff>2816</colOff>
       <row>1</row>
       <rowOff>404795</rowOff>
     </to>
@@ -984,8 +989,8 @@
       <rowOff>104795</rowOff>
     </from>
     <to>
-      <col>61</col>
-      <colOff>719138</colOff>
+      <col>62</col>
+      <colOff>2858</colOff>
       <row>1</row>
       <rowOff>428605</rowOff>
     </to>
@@ -1026,7 +1031,7 @@
     </from>
     <to>
       <col>82</col>
-      <colOff>638142</colOff>
+      <colOff>607662</colOff>
       <row>1</row>
       <rowOff>414319</rowOff>
     </to>
@@ -1067,7 +1072,7 @@
     </from>
     <to>
       <col>95</col>
-      <colOff>690563</colOff>
+      <colOff>606743</colOff>
       <row>1</row>
       <rowOff>419081</rowOff>
     </to>
@@ -1148,8 +1153,8 @@
       <rowOff>123843</rowOff>
     </from>
     <to>
-      <col>98</col>
-      <colOff>628619</colOff>
+      <col>99</col>
+      <colOff>3779</colOff>
       <row>1</row>
       <rowOff>409557</rowOff>
     </to>
@@ -1190,7 +1195,7 @@
     </from>
     <to>
       <col>99</col>
-      <colOff>723857</colOff>
+      <colOff>609557</colOff>
       <row>1</row>
       <rowOff>404795</rowOff>
     </to>
@@ -1231,7 +1236,7 @@
     </from>
     <to>
       <col>100</col>
-      <colOff>647664</colOff>
+      <colOff>609564</colOff>
       <row>1</row>
       <rowOff>419081</rowOff>
     </to>
@@ -1271,8 +1276,8 @@
       <rowOff>119081</rowOff>
     </from>
     <to>
-      <col>108</col>
-      <colOff>642904</colOff>
+      <col>109</col>
+      <colOff>2824</colOff>
       <row>1</row>
       <rowOff>414319</rowOff>
     </to>
@@ -1312,8 +1317,8 @@
       <rowOff>100034</rowOff>
     </from>
     <to>
-      <col>109</col>
-      <colOff>633381</colOff>
+      <col>110</col>
+      <colOff>921</colOff>
       <row>1</row>
       <rowOff>433367</rowOff>
     </to>
@@ -1395,7 +1400,7 @@
     </from>
     <to>
       <col>120</col>
-      <colOff>638142</colOff>
+      <colOff>607662</colOff>
       <row>1</row>
       <rowOff>433367</rowOff>
     </to>
@@ -1435,8 +1440,8 @@
       <rowOff>85748</rowOff>
     </from>
     <to>
-      <col>126</col>
-      <colOff>733380</colOff>
+      <col>127</col>
+      <colOff>1860</colOff>
       <row>1</row>
       <rowOff>447653</rowOff>
     </to>
@@ -1518,7 +1523,7 @@
     </from>
     <to>
       <col>131</col>
-      <colOff>728619</colOff>
+      <colOff>606699</colOff>
       <row>1</row>
       <rowOff>400033</rowOff>
     </to>
@@ -1559,7 +1564,7 @@
     </from>
     <to>
       <col>132</col>
-      <colOff>728619</colOff>
+      <colOff>606699</colOff>
       <row>1</row>
       <rowOff>395271</rowOff>
     </to>
@@ -1600,7 +1605,7 @@
     </from>
     <to>
       <col>133</col>
-      <colOff>714335</colOff>
+      <colOff>607655</colOff>
       <row>1</row>
       <rowOff>409557</rowOff>
     </to>
@@ -1640,8 +1645,8 @@
       <rowOff>100034</rowOff>
     </from>
     <to>
-      <col>134</col>
-      <colOff>628619</colOff>
+      <col>135</col>
+      <colOff>3779</colOff>
       <row>1</row>
       <rowOff>433367</rowOff>
     </to>
@@ -1682,7 +1687,7 @@
     </from>
     <to>
       <col>136</col>
-      <colOff>704850</colOff>
+      <colOff>605790</colOff>
       <row>1</row>
       <rowOff>476224</rowOff>
     </to>
@@ -1723,7 +1728,7 @@
     </from>
     <to>
       <col>139</col>
-      <colOff>738148</colOff>
+      <colOff>608608</colOff>
       <row>1</row>
       <rowOff>433367</rowOff>
     </to>
@@ -1764,7 +1769,7 @@
     </from>
     <to>
       <col>140</col>
-      <colOff>714329</colOff>
+      <colOff>607649</colOff>
       <row>1</row>
       <rowOff>442890</rowOff>
     </to>
@@ -1804,8 +1809,8 @@
       <rowOff>80986</rowOff>
     </from>
     <to>
-      <col>141</col>
-      <colOff>666704</colOff>
+      <col>142</col>
+      <colOff>3764</colOff>
       <row>1</row>
       <rowOff>452415</rowOff>
     </to>
@@ -1845,8 +1850,8 @@
       <rowOff>76224</rowOff>
     </from>
     <to>
-      <col>169</col>
-      <colOff>657193</colOff>
+      <col>170</col>
+      <colOff>1873</colOff>
       <row>1</row>
       <rowOff>457176</rowOff>
     </to>
@@ -1886,8 +1891,8 @@
       <rowOff>61938</rowOff>
     </from>
     <to>
-      <col>171</col>
-      <colOff>671477</colOff>
+      <col>172</col>
+      <colOff>917</colOff>
       <row>1</row>
       <rowOff>471462</rowOff>
     </to>
@@ -1927,8 +1932,8 @@
       <rowOff>71462</rowOff>
     </from>
     <to>
-      <col>180</col>
-      <colOff>657193</colOff>
+      <col>181</col>
+      <colOff>1873</colOff>
       <row>1</row>
       <rowOff>461938</rowOff>
     </to>
@@ -8623,3070 +8628,5598 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:VX2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:VX101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
+    <col width="8.88671875" customWidth="1" style="88" min="2" max="2"/>
+    <col width="18.21875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8.88671875" customWidth="1" style="88" min="6" max="6"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="13.7109375" customWidth="1" min="97" max="97"/>
-    <col width="12.140625" customWidth="1" min="105" max="105"/>
+    <col width="13.6640625" customWidth="1" min="97" max="97"/>
+    <col width="12.109375" customWidth="1" min="105" max="105"/>
     <col width="16" customWidth="1" min="120" max="120"/>
-    <col width="13.140625" customWidth="1" min="131" max="131"/>
-    <col width="20.140625" customWidth="1" min="215" max="215"/>
-    <col width="16.85546875" customWidth="1" min="216" max="216"/>
+    <col width="13.109375" customWidth="1" min="131" max="131"/>
+    <col width="20.109375" customWidth="1" min="215" max="215"/>
+    <col width="16.88671875" customWidth="1" min="216" max="216"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="HM1" s="86" t="inlineStr">
+      <c r="HM1" s="82" t="inlineStr">
         <is>
           <t>GEORISQUE</t>
         </is>
       </c>
-      <c r="MM1" s="87" t="inlineStr">
+      <c r="MM1" s="86" t="inlineStr">
         <is>
           <t>Plans de prévention des risques
 (PPR-Commune)</t>
         </is>
       </c>
-      <c r="MN1" s="88" t="n"/>
-      <c r="MO1" s="88" t="n"/>
-      <c r="MP1" s="88" t="n"/>
-      <c r="MQ1" s="88" t="n"/>
-      <c r="MR1" s="88" t="n"/>
-      <c r="MS1" s="88" t="n"/>
-      <c r="MT1" s="88" t="n"/>
-      <c r="MU1" s="88" t="n"/>
-      <c r="MV1" s="88" t="n"/>
-      <c r="MW1" s="88" t="n"/>
-      <c r="MX1" s="88" t="n"/>
-      <c r="MY1" s="88" t="n"/>
-      <c r="MZ1" s="88" t="n"/>
-      <c r="NA1" s="88" t="n"/>
-      <c r="NB1" s="88" t="n"/>
-      <c r="NC1" s="88" t="n"/>
-      <c r="ND1" s="88" t="n"/>
-      <c r="NE1" s="88" t="n"/>
-      <c r="NF1" s="88" t="n"/>
-      <c r="NG1" s="88" t="n"/>
-      <c r="NH1" s="89" t="n"/>
-      <c r="NI1" s="56" t="inlineStr">
+      <c r="MN1" s="84" t="n"/>
+      <c r="MO1" s="84" t="n"/>
+      <c r="MP1" s="84" t="n"/>
+      <c r="MQ1" s="84" t="n"/>
+      <c r="MR1" s="84" t="n"/>
+      <c r="MS1" s="84" t="n"/>
+      <c r="MT1" s="84" t="n"/>
+      <c r="MU1" s="84" t="n"/>
+      <c r="MV1" s="84" t="n"/>
+      <c r="MW1" s="84" t="n"/>
+      <c r="MX1" s="84" t="n"/>
+      <c r="MY1" s="84" t="n"/>
+      <c r="MZ1" s="84" t="n"/>
+      <c r="NA1" s="84" t="n"/>
+      <c r="NB1" s="84" t="n"/>
+      <c r="NC1" s="84" t="n"/>
+      <c r="ND1" s="84" t="n"/>
+      <c r="NE1" s="84" t="n"/>
+      <c r="NF1" s="84" t="n"/>
+      <c r="NG1" s="84" t="n"/>
+      <c r="NH1" s="85" t="n"/>
+      <c r="NI1" s="83" t="inlineStr">
         <is>
           <t>Plans de prévention des risques
 (Servitudes d'utilité publique SUP)</t>
         </is>
       </c>
-      <c r="NJ1" s="88" t="n"/>
-      <c r="NK1" s="88" t="n"/>
-      <c r="NL1" s="88" t="n"/>
-      <c r="NM1" s="88" t="n"/>
-      <c r="NN1" s="88" t="n"/>
-      <c r="NO1" s="88" t="n"/>
-      <c r="NP1" s="89" t="n"/>
-      <c r="NW1" s="90" t="inlineStr">
+      <c r="NJ1" s="84" t="n"/>
+      <c r="NK1" s="84" t="n"/>
+      <c r="NL1" s="84" t="n"/>
+      <c r="NM1" s="84" t="n"/>
+      <c r="NN1" s="84" t="n"/>
+      <c r="NO1" s="84" t="n"/>
+      <c r="NP1" s="85" t="n"/>
+      <c r="NW1" s="87" t="inlineStr">
         <is>
           <t>Sites et sols (Potentiellement) pollués</t>
         </is>
       </c>
-      <c r="NX1" s="88" t="n"/>
-      <c r="NY1" s="88" t="n"/>
-      <c r="NZ1" s="88" t="n"/>
-      <c r="OA1" s="88" t="n"/>
-      <c r="OB1" s="89" t="n"/>
+      <c r="NX1" s="84" t="n"/>
+      <c r="NY1" s="84" t="n"/>
+      <c r="NZ1" s="84" t="n"/>
+      <c r="OA1" s="84" t="n"/>
+      <c r="OB1" s="85" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="76.8" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Communes</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Postal </t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Rue</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Section </t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Numéro d'adresse</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Parcelle</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Zone Classée</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Règlement national d'urbanisme</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Plan local d'urbanisme</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Plan d'occupation des sols</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Carte communale</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Plan de sauvegarde et de mise en valeur</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Plan local d'urbanisme intercommunal</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Zone urbaine</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Zone à urbaniser, ouverte</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Zone à urbaniser, bloquée</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Zone agricole</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Zone naturelle et forestière</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Secteur ouvert à la construction</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Secteur réservé aux activités</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Constructions non autorisées</t>
         </is>
       </c>
-      <c r="V2" s="7" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>Périmètre d'application du plan de sauvegarde et mise en valeur</t>
         </is>
       </c>
-      <c r="W2" s="7" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>Zone d'aménagement concerté</t>
         </is>
       </c>
-      <c r="X2" s="7" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Zone de préemption dans un espace naturel et sensible</t>
         </is>
       </c>
-      <c r="Y2" s="7" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>Périmètre de droit de préemption urbain</t>
         </is>
       </c>
-      <c r="Z2" s="7" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>Zone d'aménagement différé</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Périmètre de développement prioritaire économie d'énergie</t>
         </is>
       </c>
-      <c r="AB2" s="7" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>Périmètre forestier : interdiction ou réglementation des plantations, plantations à réaliser et semis d'essence forestière</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>Périmètre minier de concession pour l'exploitation ou le stockage</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr">
         <is>
           <t>Zone de recherche et d'exploitation de carrière</t>
         </is>
       </c>
-      <c r="AE2" s="7" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>Périmètre des zones délimitées - divisions foncière soumises à déclaration préalable</t>
         </is>
       </c>
-      <c r="AF2" s="7" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>Périmètre de sursis à statuer</t>
         </is>
       </c>
-      <c r="AG2" s="7" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>Secteur de programme d'aménagement d'ensemble</t>
         </is>
       </c>
-      <c r="AH2" s="7" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <t>Périmètre de voisinage d'infrastructure de transport terrestre (secteur affecté par le bruit)</t>
         </is>
       </c>
-      <c r="AI2" s="7" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>Site archéologique</t>
         </is>
       </c>
-      <c r="AJ2" s="7" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <t>Zone à risque d'exposition au plomb</t>
         </is>
       </c>
-      <c r="AK2" s="7" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <t>Zones d'assainissement collectif / non collectif / eaux usées / eaux pluviales, schéma de réseaux eau et assainissement, systèmes d'élimination des déchets</t>
         </is>
       </c>
-      <c r="AL2" s="7" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>Règlement local de publicité</t>
         </is>
       </c>
-      <c r="AM2" s="7" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <t>Projet de plan de prévention des risques</t>
         </is>
       </c>
-      <c r="AN2" s="7" t="inlineStr">
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <t>Protection des rives des plans d'eau en zone de montagne</t>
         </is>
       </c>
-      <c r="AO2" s="7" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>Arrêté du préfet coordonnateur de massif</t>
         </is>
       </c>
-      <c r="AP2" s="7" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <t>Périmètre de protection des espaces agricoles et naturels péri-urbains</t>
         </is>
       </c>
-      <c r="AQ2" s="7" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <t>Plan d'exposition au bruit des aérodromes</t>
         </is>
       </c>
-      <c r="AR2" s="7" t="inlineStr">
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <t>Périmètre projet urbain partenarial</t>
         </is>
       </c>
-      <c r="AS2" s="7" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <t>Périmètres patrimoniaux d’exclusion des matériaux et énergies renouvelables pris par délibération</t>
         </is>
       </c>
-      <c r="AT2" s="7" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <t>Secteur de taxe d'aménagement</t>
         </is>
       </c>
-      <c r="AU2" s="7" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <t>Droit de préemption commercial</t>
         </is>
       </c>
-      <c r="AV2" s="7" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <t>Périmètre d'opération d'intérêt national</t>
         </is>
       </c>
-      <c r="AW2" s="7" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>Périmètre de secteur afffecté par un seuil minimal de densité</t>
         </is>
       </c>
-      <c r="AX2" s="7" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
         <is>
           <t>Schémas d'aménagement de plage</t>
         </is>
       </c>
-      <c r="AY2" s="7" t="inlineStr">
+      <c r="AY2" s="3" t="inlineStr">
         <is>
           <t>Bois ou forêts relevant du régime forestier</t>
         </is>
       </c>
-      <c r="AZ2" s="7" t="inlineStr">
+      <c r="AZ2" s="3" t="inlineStr">
         <is>
           <t>Secteurs d'information sur les sols</t>
         </is>
       </c>
-      <c r="BA2" s="7" t="inlineStr">
+      <c r="BA2" s="3" t="inlineStr">
         <is>
           <t>Périmètres de projets Association Foncière Urbaine de Projet</t>
         </is>
       </c>
-      <c r="BB2" s="7" t="inlineStr">
+      <c r="BB2" s="3" t="inlineStr">
         <is>
           <t>Bien inscrit au patrimoine mondial</t>
         </is>
       </c>
-      <c r="BC2" s="7" t="inlineStr">
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>Bande de recul le long des axes à grande circulation</t>
         </is>
       </c>
-      <c r="BD2" s="7" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr">
         <is>
           <t>Secteurs délimités par délibération de l'autorité compétente en matière d'urbanisme, dans lesquels certaines opérations sont soumises à autorisation d'urbanisme</t>
         </is>
       </c>
-      <c r="BE2" s="7" t="inlineStr">
+      <c r="BE2" s="3" t="inlineStr">
         <is>
           <t>Secteur d’obligation légale de débroussaillement (OLD) en prévention des incendies</t>
         </is>
       </c>
-      <c r="BF2" s="7" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr">
         <is>
           <t>Emprise ou localisation des immeubles bâtis ou non bâtis classés ou inscrits au titre des monuments historiques</t>
         </is>
       </c>
-      <c r="BG2" s="7" t="inlineStr">
+      <c r="BG2" s="3" t="inlineStr">
         <is>
           <t>Périmètre d’application d’une pièce écrite territorialisée relative aux annexes</t>
         </is>
       </c>
-      <c r="BH2" s="7" t="inlineStr">
+      <c r="BH2" s="3" t="inlineStr">
         <is>
           <t>Périmètre d’annulation partielle du document d’urbanisme</t>
         </is>
       </c>
-      <c r="BI2" s="7" t="inlineStr">
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>Autres périmètres d'informations</t>
         </is>
       </c>
-      <c r="BJ2" s="7" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>Diversité commerciale à protéger ou à développer</t>
         </is>
       </c>
-      <c r="BK2" s="7" t="inlineStr">
+      <c r="BK2" s="3" t="inlineStr">
         <is>
           <t>Secteur à programme de logements mixité sociale en zone U et AU</t>
         </is>
       </c>
-      <c r="BL2" s="7" t="inlineStr">
+      <c r="BL2" s="3" t="inlineStr">
         <is>
           <t>Secteur avec taille minimale des logements en zone U et AU</t>
         </is>
       </c>
-      <c r="BM2" s="7" t="inlineStr">
+      <c r="BM2" s="3" t="inlineStr">
         <is>
           <t>Majoration des volumes constructibles</t>
         </is>
       </c>
-      <c r="BN2" s="7" t="inlineStr">
+      <c r="BN2" s="3" t="inlineStr">
         <is>
           <t>Mixité des destinations ou sous-destinations</t>
         </is>
       </c>
-      <c r="BO2" s="7" t="inlineStr">
+      <c r="BO2" s="3" t="inlineStr">
         <is>
           <t>Règles différenciées entre le rez-de-chaussée et les étages supérieurs des constructions</t>
         </is>
       </c>
-      <c r="BP2" s="7" t="inlineStr">
+      <c r="BP2" s="3" t="inlineStr">
         <is>
           <t>Réalisation d’espaces libres, plantations, aires de jeux et de loisir</t>
         </is>
       </c>
-      <c r="BQ2" s="7" t="inlineStr">
+      <c r="BQ2" s="3" t="inlineStr">
         <is>
           <t>Espace vert non protégé à requalifier</t>
         </is>
       </c>
-      <c r="BR2" s="7" t="inlineStr">
+      <c r="BR2" s="3" t="inlineStr">
         <is>
           <t>Place, cour, ou autre espace libre à dominante minérale non protégé à requalifier</t>
         </is>
       </c>
-      <c r="BS2" s="7" t="inlineStr">
+      <c r="BS2" s="3" t="inlineStr">
         <is>
           <t>Secteur dans lequel toutes les constructions nouvelles de logements sont à usage exclusif de résidence principale</t>
         </is>
       </c>
-      <c r="BT2" s="7" t="inlineStr">
+      <c r="BT2" s="3" t="inlineStr">
         <is>
           <t>Espace boisé classé</t>
         </is>
       </c>
-      <c r="BU2" s="7" t="inlineStr">
+      <c r="BU2" s="3" t="inlineStr">
         <is>
           <t>Espace boisé classé à protéger ou conserver</t>
         </is>
       </c>
-      <c r="BV2" s="7" t="inlineStr">
+      <c r="BV2" s="3" t="inlineStr">
         <is>
           <t>Elément intérieur particulier protégé, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="BW2" s="7" t="inlineStr">
+      <c r="BW2" s="3" t="inlineStr">
         <is>
           <t>Elément extérieur particulier protégé à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="BX2" s="7" t="inlineStr">
+      <c r="BX2" s="3" t="inlineStr">
         <is>
           <t>Arbre remarquable ou autre élément naturel protégé à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="BY2" s="7" t="inlineStr">
+      <c r="BY2" s="3" t="inlineStr">
         <is>
           <t>Point d'eau ou source protégé, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="BZ2" s="7" t="inlineStr">
+      <c r="BZ2" s="3" t="inlineStr">
         <is>
           <t>Mur de soutènemenr, rempart ou mur de clôture protégé, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CA2" s="7" t="inlineStr">
+      <c r="CA2" s="3" t="inlineStr">
         <is>
           <t>Séquence, composition, ordonnance architecturale ou urbaine protégée, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CB2" s="7" t="inlineStr">
+      <c r="CB2" s="3" t="inlineStr">
         <is>
           <t>Séquence naturelle protégée (front rocheux, falaise, etc.), à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CC2" s="7" t="inlineStr">
+      <c r="CC2" s="3" t="inlineStr">
         <is>
           <t>Séquence, composition ou ordonnance végétale s'ensemble protégée, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CD2" s="7" t="inlineStr">
+      <c r="CD2" s="3" t="inlineStr">
         <is>
           <t>Passage d'eau souterrain protégé, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CE2" s="7" t="inlineStr">
+      <c r="CE2" s="3" t="inlineStr">
         <is>
           <t>Unité urbanistique ou paysagère soumise à des dispositions spécifiques</t>
         </is>
       </c>
-      <c r="CF2" s="7" t="inlineStr">
+      <c r="CF2" s="3" t="inlineStr">
         <is>
           <t>Patrimoine bâti, paysager ou éléments de paysages à protéger pour des motifs d'ordre culturel, historique, architectural ou écologique</t>
         </is>
       </c>
-      <c r="CG2" s="7" t="inlineStr">
+      <c r="CG2" s="3" t="inlineStr">
         <is>
           <t>Immeuble bâti dont les parties intérieures sont protégées en totalité, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CH2" s="7" t="inlineStr">
+      <c r="CH2" s="3" t="inlineStr">
         <is>
           <t>Immeuble bâti dont les parties extérieures sont protégées, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CI2" s="7" t="inlineStr">
+      <c r="CI2" s="3" t="inlineStr">
         <is>
           <t>Parc ou jardin de pleine terre protégé, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CJ2" s="7" t="inlineStr">
+      <c r="CJ2" s="3" t="inlineStr">
         <is>
           <t>Espace libre à dominante végétale protégé à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CK2" s="7" t="inlineStr">
+      <c r="CK2" s="3" t="inlineStr">
         <is>
           <t>Place, cour ou autre espace libre à dominante minérale protégé, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CL2" s="7" t="inlineStr">
+      <c r="CL2" s="3" t="inlineStr">
         <is>
           <t>Cours d'eau, réseau hydraulique ou étendue aquatique protégé, à conserver, restaurer et mettre en valeur</t>
         </is>
       </c>
-      <c r="CM2" s="7" t="inlineStr">
+      <c r="CM2" s="3" t="inlineStr">
         <is>
           <t>Espace vert non protégé à requalifier</t>
         </is>
       </c>
-      <c r="CN2" s="7" t="inlineStr">
+      <c r="CN2" s="3" t="inlineStr">
         <is>
           <t>Place, cour, ou autre espace libre à dominante minérale non protégé à requalifier</t>
         </is>
       </c>
-      <c r="CO2" s="7" t="inlineStr">
+      <c r="CO2" s="3" t="inlineStr">
         <is>
           <t>Immeuble bâti non protégé soumis à des dispositions spécifiques ou des règles générales localisées</t>
         </is>
       </c>
-      <c r="CP2" s="7" t="inlineStr">
+      <c r="CP2" s="3" t="inlineStr">
         <is>
           <t>Immeuble non bâti ou espace libre non protégé soumis à des dispositions spécifiques ou des règles générales localisées</t>
         </is>
       </c>
-      <c r="CQ2" s="7" t="inlineStr">
+      <c r="CQ2" s="3" t="inlineStr">
         <is>
           <t>Terrain cultivé ou non bâti à protéger en zone urbaine</t>
         </is>
       </c>
-      <c r="CR2" s="7" t="inlineStr">
+      <c r="CR2" s="3" t="inlineStr">
         <is>
           <t>Éléments de continuité écologique et trame verte et bleue</t>
         </is>
       </c>
-      <c r="CS2" s="7" t="inlineStr">
+      <c r="CS2" s="3" t="inlineStr">
         <is>
           <t>Espaces remarquables du littoral</t>
         </is>
       </c>
-      <c r="CT2" s="7" t="inlineStr">
+      <c r="CT2" s="3" t="inlineStr">
         <is>
           <t>Exclusion protection de plans d’eau de faible importance</t>
         </is>
       </c>
-      <c r="CU2" s="7" t="inlineStr">
+      <c r="CU2" s="3" t="inlineStr">
         <is>
           <t>Secteur de dérogation aux protections des rives des plans d'eau en zone de montagne</t>
         </is>
       </c>
-      <c r="CV2" s="7" t="inlineStr">
+      <c r="CV2" s="3" t="inlineStr">
         <is>
           <t>Espaces, paysage et milieux caractéristiques du patrimoine naturel et culturel montagnard à préserver</t>
         </is>
       </c>
-      <c r="CW2" s="7" t="inlineStr">
+      <c r="CW2" s="3" t="inlineStr">
         <is>
           <t>Terres nécessaires au maintien et au développement des activités agricoles pastorales et forestières à préserver</t>
         </is>
       </c>
-      <c r="CX2" s="7" t="inlineStr">
+      <c r="CX2" s="3" t="inlineStr">
         <is>
           <t>Coefficient de biotope par surface</t>
         </is>
       </c>
-      <c r="CY2" s="7" t="inlineStr">
+      <c r="CY2" s="3" t="inlineStr">
         <is>
           <t>Constructibilité espace boisé antérieur au 20ème siècle</t>
         </is>
       </c>
-      <c r="CZ2" s="7" t="inlineStr">
+      <c r="CZ2" s="3" t="inlineStr">
         <is>
           <t>Zone exposée au recul du trait de côte à l'horizon de trente ans</t>
         </is>
       </c>
-      <c r="DA2" s="7" t="inlineStr">
+      <c r="DA2" s="3" t="inlineStr">
         <is>
           <t>Immeuble ou partie d'immeuble dont la modification peut être imposée à l'occasion d'opérations d'aménagement publiques ou privées</t>
         </is>
       </c>
-      <c r="DB2" s="7" t="inlineStr">
+      <c r="DB2" s="3" t="inlineStr">
         <is>
           <t>Secteur avec disposition de reconstruction/démolition</t>
         </is>
       </c>
-      <c r="DC2" s="7" t="inlineStr">
+      <c r="DC2" s="3" t="inlineStr">
         <is>
           <t>Immeuble ou partie d'immeuble dont la démolition peut être imposée à l'occasion d'opérations d'aménagement publiques ou privées</t>
         </is>
       </c>
-      <c r="DD2" s="7" t="inlineStr">
+      <c r="DD2" s="3" t="inlineStr">
         <is>
           <t>Périmètre issu des plan de déplacements urbains sur obligation de stationnement</t>
         </is>
       </c>
-      <c r="DE2" s="7" t="inlineStr">
+      <c r="DE2" s="3" t="inlineStr">
         <is>
           <t>Limite maximale d'implantation de construction</t>
         </is>
       </c>
-      <c r="DF2" s="7" t="inlineStr">
+      <c r="DF2" s="3" t="inlineStr">
         <is>
           <t>Limite imposée d'implantation de construction</t>
         </is>
       </c>
-      <c r="DG2" s="7" t="inlineStr">
+      <c r="DG2" s="3" t="inlineStr">
         <is>
           <t>Règles d'implantation des constructions</t>
         </is>
       </c>
-      <c r="DH2" s="7" t="inlineStr">
+      <c r="DH2" s="3" t="inlineStr">
         <is>
           <t>Constructions et installations nécessaires à des équipements collectifs en zone A ou N</t>
         </is>
       </c>
-      <c r="DI2" s="7" t="inlineStr">
+      <c r="DI2" s="3" t="inlineStr">
         <is>
           <t>Secteur à transfert de constructibilité en zone N</t>
         </is>
       </c>
-      <c r="DJ2" s="7" t="inlineStr">
+      <c r="DJ2" s="3" t="inlineStr">
         <is>
           <t>Secteur avec densité minimale de construction</t>
         </is>
       </c>
-      <c r="DK2" s="7" t="inlineStr">
+      <c r="DK2" s="3" t="inlineStr">
         <is>
           <t>Emprise au sol</t>
         </is>
       </c>
-      <c r="DL2" s="7" t="inlineStr">
+      <c r="DL2" s="3" t="inlineStr">
         <is>
           <t>Hauteur maximale de façade</t>
         </is>
       </c>
-      <c r="DM2" s="7" t="inlineStr">
+      <c r="DM2" s="3" t="inlineStr">
         <is>
           <t>Hauteur maximale de faîtage ou de construction</t>
         </is>
       </c>
-      <c r="DN2" s="7" t="inlineStr">
+      <c r="DN2" s="3" t="inlineStr">
         <is>
           <t>Hauteur imposée de façade</t>
         </is>
       </c>
-      <c r="DO2" s="7" t="inlineStr">
+      <c r="DO2" s="3" t="inlineStr">
         <is>
           <t>Point de vue, perspective à préserver et à mettre en valeur</t>
         </is>
       </c>
-      <c r="DP2" s="7" t="inlineStr">
+      <c r="DP2" s="3" t="inlineStr">
         <is>
           <t>Aspect extérieur</t>
         </is>
       </c>
-      <c r="DQ2" s="7" t="inlineStr">
+      <c r="DQ2" s="3" t="inlineStr">
         <is>
           <t>Stationnement</t>
         </is>
       </c>
-      <c r="DR2" s="7" t="inlineStr">
+      <c r="DR2" s="3" t="inlineStr">
         <is>
           <t>Secteur de ZAC avec surfaces de plancher déterminées</t>
         </is>
       </c>
-      <c r="DS2" s="7" t="inlineStr">
+      <c r="DS2" s="3" t="inlineStr">
         <is>
           <t>Secteur de plan de masse</t>
         </is>
       </c>
-      <c r="DT2" s="7" t="inlineStr">
+      <c r="DT2" s="3" t="inlineStr">
         <is>
           <t>Périmètre comportant des orientations d’aménagement et de programmation (OAP)</t>
         </is>
       </c>
-      <c r="DU2" s="7" t="inlineStr">
+      <c r="DU2" s="3" t="inlineStr">
         <is>
           <t>Opération d'ensemble imposée en zone AU</t>
         </is>
       </c>
-      <c r="DV2" s="7" t="inlineStr">
+      <c r="DV2" s="3" t="inlineStr">
         <is>
           <t>Autres prescriptions</t>
         </is>
       </c>
-      <c r="DW2" s="7" t="inlineStr">
+      <c r="DW2" s="3" t="inlineStr">
         <is>
           <t>Emplacement réservé</t>
         </is>
       </c>
-      <c r="DX2" s="7" t="inlineStr">
+      <c r="DX2" s="3" t="inlineStr">
         <is>
           <t>Passage ou liaison piétonne à maintenir ou à créer</t>
         </is>
       </c>
-      <c r="DY2" s="7" t="inlineStr">
+      <c r="DY2" s="3" t="inlineStr">
         <is>
           <t>Secteur de performance énergétique</t>
         </is>
       </c>
-      <c r="DZ2" s="7" t="inlineStr">
+      <c r="DZ2" s="3" t="inlineStr">
         <is>
           <t>Secteur d’aménagement numérique</t>
         </is>
       </c>
-      <c r="EA2" s="8" t="inlineStr">
+      <c r="EA2" s="4" t="inlineStr">
         <is>
           <t>Conditions de desserte</t>
         </is>
       </c>
-      <c r="EB2" s="7" t="inlineStr">
+      <c r="EB2" s="3" t="inlineStr">
         <is>
           <t>Desserte par les réseaux</t>
         </is>
       </c>
-      <c r="EC2" s="7" t="inlineStr">
+      <c r="EC2" s="3" t="inlineStr">
         <is>
           <t>Mesures pour limiter l'imperméabilisation des sols</t>
         </is>
       </c>
-      <c r="ED2" s="7" t="inlineStr">
+      <c r="ED2" s="3" t="inlineStr">
         <is>
           <t>Infrastructures et équipements logistiques à préserver ou à développer en zones U et AU</t>
         </is>
       </c>
-      <c r="EE2" s="7" t="inlineStr">
+      <c r="EE2" s="3" t="inlineStr">
         <is>
           <t>Dérogation à l’article L.111-6 pour l’implantation des constructions le long des grands axes routiers</t>
         </is>
       </c>
-      <c r="EF2" s="7" t="inlineStr">
+      <c r="EF2" s="3" t="inlineStr">
         <is>
           <t>Secteur d’implantation d’installations de production d'énergies renouvelables, et leurs ouvrages de raccordement, soumises à conditions</t>
         </is>
       </c>
-      <c r="EG2" s="7" t="inlineStr">
+      <c r="EG2" s="3" t="inlineStr">
         <is>
           <t>Limitation de la constructibilité pour des raisons environnementales, de risques, d’intérêt général</t>
         </is>
       </c>
-      <c r="EH2" s="7" t="inlineStr">
+      <c r="EH2" s="3" t="inlineStr">
         <is>
           <t>Zone à aménager en vue de la pratique du ski</t>
         </is>
       </c>
-      <c r="EI2" s="7" t="inlineStr">
+      <c r="EI2" s="3" t="inlineStr">
         <is>
           <t>Secteur protégé en raison de la richesse du sol et du sous-sol</t>
         </is>
       </c>
-      <c r="EJ2" s="7" t="inlineStr">
+      <c r="EJ2" s="3" t="inlineStr">
         <is>
           <t>Interdiction types d’activités, destinations, sous-destinations</t>
         </is>
       </c>
-      <c r="EK2" s="7" t="inlineStr">
+      <c r="EK2" s="3" t="inlineStr">
         <is>
           <t>Autorisation sous conditions types d’activités, destinations, sous-destinations</t>
         </is>
       </c>
-      <c r="EL2" s="7" t="inlineStr">
+      <c r="EL2" s="3" t="inlineStr">
         <is>
           <t>Autres prescriptions</t>
         </is>
       </c>
-      <c r="EM2" s="7" t="inlineStr">
+      <c r="EM2" s="3" t="inlineStr">
         <is>
           <t>Mises en compatibilité</t>
         </is>
       </c>
-      <c r="EN2" s="7" t="inlineStr">
+      <c r="EN2" s="3" t="inlineStr">
         <is>
           <t>A1 - Servitude de protection des bois et forêts relevant du régime forestier à Mayotte</t>
         </is>
       </c>
-      <c r="EO2" s="7" t="inlineStr">
+      <c r="EO2" s="3" t="inlineStr">
         <is>
           <t>A7 - Servitude relative aux forêts dites de protection</t>
         </is>
       </c>
-      <c r="EP2" s="7" t="inlineStr">
+      <c r="EP2" s="3" t="inlineStr">
         <is>
           <t>A8 - Servitudes résultant de la mise en défens des terrains et pâturages en montagne et relatives à la protection des dunes du Pas-de-Calais</t>
         </is>
       </c>
-      <c r="EQ2" s="7" t="inlineStr">
+      <c r="EQ2" s="3" t="inlineStr">
         <is>
           <t>EL9 - Servitude de passage des piétons sur le littoral</t>
         </is>
       </c>
-      <c r="ER2" s="7" t="inlineStr">
+      <c r="ER2" s="3" t="inlineStr">
         <is>
           <t>AS1 - Servitudes résultant de l’instauration de périmètres de protection autour des captages d’eaux destinés à l’alimentation en eau potable et des sources minérales naturelles - périmètre de protection immédiate</t>
         </is>
       </c>
-      <c r="ES2" s="7" t="inlineStr">
+      <c r="ES2" s="3" t="inlineStr">
         <is>
           <t>AS1 - Servitudes résultant de l’instauration de périmètres de protection autour des captages d’eaux destinés à l’alimentation en eau potable et des sources minérales naturelles - périmètre de protection rapprochée</t>
         </is>
       </c>
-      <c r="ET2" s="7" t="inlineStr">
+      <c r="ET2" s="3" t="inlineStr">
         <is>
           <t>AS1 - Servitudes résultant de l’instauration de périmètres de protection autour des captages d’eaux destinés à l’alimentation en eau potable et des sources minérales naturelles - périmètre de protection éloignée</t>
         </is>
       </c>
-      <c r="EU2" s="7" t="inlineStr">
+      <c r="EU2" s="3" t="inlineStr">
         <is>
           <t>AS1 - Servitudes résultant de l’instauration de périmètres de protection autour des captages d’eaux destinés à l’alimentation en eau potable et des sources minérales naturelles - périmètre de protection eau minérale</t>
         </is>
       </c>
-      <c r="EV2" s="7" t="inlineStr">
+      <c r="EV2" s="3" t="inlineStr">
         <is>
           <t>A4 - Servitude de passage dans le lit ou sur les berges de cours d’eau</t>
         </is>
       </c>
-      <c r="EW2" s="7" t="inlineStr">
+      <c r="EW2" s="3" t="inlineStr">
         <is>
           <t>AC3 - Réserves naturelles et périmètres de protection autour des réserves naturelles</t>
         </is>
       </c>
-      <c r="EX2" s="7" t="inlineStr">
+      <c r="EX2" s="3" t="inlineStr">
         <is>
           <t>EL10 - Cœur de parc national</t>
         </is>
       </c>
-      <c r="EY2" s="7" t="inlineStr">
+      <c r="EY2" s="3" t="inlineStr">
         <is>
           <t>A9 - Zones agricoles protégées</t>
         </is>
       </c>
-      <c r="EZ2" s="7" t="inlineStr">
+      <c r="EZ2" s="3" t="inlineStr">
         <is>
           <t>A10 - Zone de protection naturelle, agricole et forestière du plateau de Saclay</t>
         </is>
       </c>
-      <c r="FA2" s="7" t="inlineStr">
+      <c r="FA2" s="3" t="inlineStr">
         <is>
           <t>AC1 - Servitudes relatives aux monuments historiques (immeubles classés et inscrits, abords des monuments historiques) - Périmètre des abords</t>
         </is>
       </c>
-      <c r="FB2" s="7" t="inlineStr">
+      <c r="FB2" s="3" t="inlineStr">
         <is>
           <t>AC1 - Servitudes relatives aux monuments historiques (immeubles classés et inscrits, abords des monuments historiques) - Monuments historiques</t>
         </is>
       </c>
-      <c r="FC2" s="7" t="inlineStr">
+      <c r="FC2" s="3" t="inlineStr">
         <is>
           <t>AC2 - Servitudes relatives aux sites inscrits et classés</t>
         </is>
       </c>
-      <c r="FD2" s="7" t="inlineStr">
+      <c r="FD2" s="3" t="inlineStr">
         <is>
           <t>AC4 - Sites patrimoniaux remarquables (SPR)</t>
         </is>
       </c>
-      <c r="FE2" s="7" t="inlineStr">
+      <c r="FE2" s="3" t="inlineStr">
         <is>
           <t>AC4bis - Plans de valorisation de l'architecture et du patrimoine (PVAP)</t>
         </is>
       </c>
-      <c r="FF2" s="7" t="inlineStr">
+      <c r="FF2" s="3" t="inlineStr">
         <is>
           <t>JS1 - Servitude de protection des équipements sportifs</t>
         </is>
       </c>
-      <c r="FG2" s="7" t="inlineStr">
+      <c r="FG2" s="3" t="inlineStr">
         <is>
           <t>I4 - Servitudes relatives aux ouvrages de transport et de distribution d’électricité - Canalisations électriques</t>
         </is>
       </c>
-      <c r="FH2" s="7" t="inlineStr">
+      <c r="FH2" s="3" t="inlineStr">
         <is>
           <t>I5 - Servitudes relatives à l'établissement des canalisations de distribution de gaz</t>
         </is>
       </c>
-      <c r="FI2" s="7" t="inlineStr">
+      <c r="FI2" s="3" t="inlineStr">
         <is>
           <t>I2 - Servitudes liées aux installations hydrauliques concédées</t>
         </is>
       </c>
-      <c r="FJ2" s="7" t="inlineStr">
+      <c r="FJ2" s="3" t="inlineStr">
         <is>
           <t>I9 - Servitudes relatives aux canalisations de transport et de distribution de chaleur et de froid</t>
         </is>
       </c>
-      <c r="FK2" s="7" t="inlineStr">
+      <c r="FK2" s="3" t="inlineStr">
         <is>
           <t>I6 - Servitudes relatives à l'exploration et l'exploitation des mines et carrières</t>
         </is>
       </c>
-      <c r="FL2" s="7" t="inlineStr">
+      <c r="FL2" s="3" t="inlineStr">
         <is>
           <t>I3 - Servitude relative à l’établissement des canalisations de transport de gaz naturel ou assimilé, d’hydrocarbures et de produits chimiques - Zone de protection</t>
         </is>
       </c>
-      <c r="FM2" s="7" t="inlineStr">
+      <c r="FM2" s="3" t="inlineStr">
         <is>
           <t>I3 - Servitude relative à l’établissement des canalisations de transport de gaz naturel ou assimilé, d’hydrocarbures et de produits chimiques - Zone de passage</t>
         </is>
       </c>
-      <c r="FN2" s="7" t="inlineStr">
+      <c r="FN2" s="3" t="inlineStr">
         <is>
           <t>A2 - Servitudes de passage des conduites souterraines d'irrigation</t>
         </is>
       </c>
-      <c r="FO2" s="7" t="inlineStr">
+      <c r="FO2" s="3" t="inlineStr">
         <is>
           <t>A3 - Servitudes de passage des engins mécaniques d'entretien et de dépôt pour l’entretien des canaux d'irrigation et de certains émissaires d’assainissement</t>
         </is>
       </c>
-      <c r="FP2" s="7" t="inlineStr">
+      <c r="FP2" s="3" t="inlineStr">
         <is>
           <t>A5 - Servitudes pour l’établissement des canalisations publiques d’eau et d’assainissement</t>
         </is>
       </c>
-      <c r="FQ2" s="7" t="inlineStr">
+      <c r="FQ2" s="3" t="inlineStr">
         <is>
           <t>A6 - Servitude d'écoulement des eaux nuisibles attachées aux travaux d'assainissement des terres par le drainage</t>
         </is>
       </c>
-      <c r="FR2" s="7" t="inlineStr">
+      <c r="FR2" s="3" t="inlineStr">
         <is>
           <t>EL3 - Servitude de halage et de marchepied - Halage</t>
         </is>
       </c>
-      <c r="FS2" s="7" t="inlineStr">
+      <c r="FS2" s="3" t="inlineStr">
         <is>
           <t>EL3 - Servitude de halage et de marchepied - Marchepied</t>
         </is>
       </c>
-      <c r="FT2" s="7" t="inlineStr">
+      <c r="FT2" s="3" t="inlineStr">
         <is>
           <t>EL8 - Servitudes de champs de vue et de visibilité pour les établissements de signalisation maritime (ESM)</t>
         </is>
       </c>
-      <c r="FU2" s="7" t="inlineStr">
+      <c r="FU2" s="3" t="inlineStr">
         <is>
           <t>T1 - Servitudes de protection du domaine public ferroviaire</t>
         </is>
       </c>
-      <c r="FV2" s="7" t="inlineStr">
+      <c r="FV2" s="3" t="inlineStr">
         <is>
           <t>T3 - Servitudes en tréfonds</t>
         </is>
       </c>
-      <c r="FW2" s="7" t="inlineStr">
+      <c r="FW2" s="3" t="inlineStr">
         <is>
           <t>EL5 - Servitude de visibilité sur les voies publiques</t>
         </is>
       </c>
-      <c r="FX2" s="7" t="inlineStr">
+      <c r="FX2" s="3" t="inlineStr">
         <is>
           <t>EL6 - Servitude grévant les terrains nécessaires aux routes nationales et aux autoroutes</t>
         </is>
       </c>
-      <c r="FY2" s="7" t="inlineStr">
+      <c r="FY2" s="3" t="inlineStr">
         <is>
           <t>EL7 - Servitudes d'alignement des voies publiques</t>
         </is>
       </c>
-      <c r="FZ2" s="7" t="inlineStr">
+      <c r="FZ2" s="3" t="inlineStr">
         <is>
           <t>EL11 - Servitude relative aux interdictions d'accès grevant les propriétés limitrophes des autoroutes, routes express et déviations d'agglomération</t>
         </is>
       </c>
-      <c r="GA2" s="7" t="inlineStr">
+      <c r="GA2" s="3" t="inlineStr">
         <is>
           <t>T4 - Servitude aéronautique de balisage</t>
         </is>
       </c>
-      <c r="GB2" s="7" t="inlineStr">
+      <c r="GB2" s="3" t="inlineStr">
         <is>
           <t>T5 - Servitudes aéronautiques de dégagement (civile)</t>
         </is>
       </c>
-      <c r="GC2" s="7" t="inlineStr">
+      <c r="GC2" s="3" t="inlineStr">
         <is>
           <t>T6 - Servitude grévant les terrains nécessaires aux besoins de la navigation aérienne</t>
         </is>
       </c>
-      <c r="GD2" s="7" t="inlineStr">
+      <c r="GD2" s="3" t="inlineStr">
         <is>
           <t>T7 - Servitudes établies à l'extérieur des zones de dégagement</t>
         </is>
       </c>
-      <c r="GE2" s="7" t="inlineStr">
+      <c r="GE2" s="3" t="inlineStr">
         <is>
           <t>EL4 - Servitude relative au développement et à la protection des montagnes</t>
         </is>
       </c>
-      <c r="GF2" s="7" t="inlineStr">
+      <c r="GF2" s="3" t="inlineStr">
         <is>
           <t>T2 - Servitude de survol au profit des téléphériques</t>
         </is>
       </c>
-      <c r="GG2" s="7" t="inlineStr">
+      <c r="GG2" s="3" t="inlineStr">
         <is>
           <t>T9 - Servitude au profit des transports guidés par câble en milieu urbain</t>
         </is>
       </c>
-      <c r="GH2" s="7" t="inlineStr">
+      <c r="GH2" s="3" t="inlineStr">
         <is>
           <t>PT1 - Servitudes de protection des centres radioélectriques d’émission et de réception contre les perturbations électromagnétiques - Zone de garde</t>
         </is>
       </c>
-      <c r="GI2" s="7" t="inlineStr">
+      <c r="GI2" s="3" t="inlineStr">
         <is>
           <t>PT1 - Servitudes de protection des centres radioélectriques d’émission et de réception contre les perturbations électromagnétiques - Zone de protection</t>
         </is>
       </c>
-      <c r="GJ2" s="7" t="inlineStr">
+      <c r="GJ2" s="3" t="inlineStr">
         <is>
           <t>PT2 - Servitudes de protection des centres radioélectriques d’émission et de réception contre les obstacles physiques - Zone primaire de dégagement</t>
         </is>
       </c>
-      <c r="GK2" s="7" t="inlineStr">
+      <c r="GK2" s="3" t="inlineStr">
         <is>
           <t>PT2 - Servitudes de protection des centres radioélectriques d’émission et de réception contre les obstacles physiques - Zone secondaire de dégagement</t>
         </is>
       </c>
-      <c r="GL2" s="7" t="inlineStr">
+      <c r="GL2" s="3" t="inlineStr">
         <is>
           <t>PT3 - Servitude attachée aux réseaux de télécommunications</t>
         </is>
       </c>
-      <c r="GM2" s="7" t="inlineStr">
+      <c r="GM2" s="3" t="inlineStr">
         <is>
           <t>AR1 - Servitudes de champs de vue concernant les postes électro-sémaphoriques de la marine nationale</t>
         </is>
       </c>
-      <c r="GN2" s="7" t="inlineStr">
+      <c r="GN2" s="3" t="inlineStr">
         <is>
           <t>AR2 - Servitudes de champs de vue concernant les postes militaires de défense des côtes et de sécurité de la navigation</t>
         </is>
       </c>
-      <c r="GO2" s="7" t="inlineStr">
+      <c r="GO2" s="3" t="inlineStr">
         <is>
           <t>AR3 - Servitude autour des magasins et établissements servant à la conservation, à la manipulation ou à la fabrication des poudres, munitions, artifices ou explosifs - Zones de prohibition</t>
         </is>
       </c>
-      <c r="GP2" s="7" t="inlineStr">
+      <c r="GP2" s="3" t="inlineStr">
         <is>
           <t>AR3 - Servitude autour des magasins et établissements servant à la conservation, à la manipulation ou à la fabrication des poudres, munitions, artifices ou explosifs - Zones d'isolement</t>
         </is>
       </c>
-      <c r="GQ2" s="7" t="inlineStr">
+      <c r="GQ2" s="3" t="inlineStr">
         <is>
           <t>AR4 - Servitudes concernant l'établissement de terrains d'atterrissage destinés en partie ou en totalité à l'armée de l'air</t>
         </is>
       </c>
-      <c r="GR2" s="7" t="inlineStr">
+      <c r="GR2" s="3" t="inlineStr">
         <is>
           <t>AR5 - Servitudes autour des installations de défense autres que celles concernées par les SUP AR1 à AR4 et AR6</t>
         </is>
       </c>
-      <c r="GS2" s="7" t="inlineStr">
+      <c r="GS2" s="3" t="inlineStr">
         <is>
           <t>AR6 - Servitudes aux abords des champs de tir</t>
         </is>
       </c>
-      <c r="GT2" s="7" t="inlineStr">
+      <c r="GT2" s="3" t="inlineStr">
         <is>
           <t>INT1 - Servitudes instituées au voisinage des cimetières</t>
         </is>
       </c>
-      <c r="GU2" s="7" t="inlineStr">
+      <c r="GU2" s="3" t="inlineStr">
         <is>
           <t>AS2 - Servitudes résultant de l’instauration de périmètres de protection autour des établissements de conchyliculture et d’aquaculture et des gisements coquilliers</t>
         </is>
       </c>
-      <c r="GV2" s="7" t="inlineStr">
+      <c r="GV2" s="3" t="inlineStr">
         <is>
           <t>EL2bis - Servitude qui concerne la Loire et ses affluents</t>
         </is>
       </c>
-      <c r="GW2" s="7" t="inlineStr">
+      <c r="GW2" s="3" t="inlineStr">
         <is>
           <t>PM1 - Plans de prévention des risques naturels prévisibles (PPRNP) et plans de prévention de risques miniers (PPRM) et documents valant PPRNP</t>
         </is>
       </c>
-      <c r="GX2" s="7" t="inlineStr">
+      <c r="GX2" s="3" t="inlineStr">
         <is>
           <t>PM1bis - Servitude d'inondation pour la rétention des crues du Rhin</t>
         </is>
       </c>
-      <c r="GY2" s="7" t="inlineStr">
+      <c r="GY2" s="3" t="inlineStr">
         <is>
           <t>PM2 - Servitudes autour des installations classées pour la protection de l’environnement et sur des sites et sols pollués, de stockage de déchets ou d’anciennes carrières</t>
         </is>
       </c>
-      <c r="GZ2" s="7" t="inlineStr">
+      <c r="GZ2" s="3" t="inlineStr">
         <is>
           <t>PM3 - Plans de prévention des risques technologiques (PPRT)</t>
         </is>
       </c>
-      <c r="HA2" s="7" t="inlineStr">
+      <c r="HA2" s="3" t="inlineStr">
         <is>
           <t>PM4 - Servitude relative aux zones de rétention temporaire des eaux de crues ou de ruissellement, de mobilité d’un cours d’eau et aux zones dites "stratégiques pour la gestion de l’eau"</t>
         </is>
       </c>
-      <c r="HB2" s="7" t="inlineStr">
+      <c r="HB2" s="3" t="inlineStr">
         <is>
           <t>PM5 - Servitudes visant à ne pas aggraver les risques pour la sécurité publique en présence d’un ouvrages hydraulique</t>
         </is>
       </c>
-      <c r="HC2" s="7" t="inlineStr">
+      <c r="HC2" s="3" t="inlineStr">
         <is>
           <t>PM6 - Servitudes autour des installations nucléaires de base</t>
         </is>
       </c>
-      <c r="HD2" s="7" t="inlineStr">
+      <c r="HD2" s="3" t="inlineStr">
         <is>
           <t>PM7 - Servitudes relatives aux ouvrages ou infrastructures permettant de prévenir les inondations ou les submersions</t>
         </is>
       </c>
-      <c r="HE2" s="7" t="inlineStr">
+      <c r="HE2" s="3" t="inlineStr">
         <is>
           <t>PM8 - Servitudes relatives à la création, la continuité, la pérennité et l’entretien des équipements de défense des forêts contre les incendies (DFCI)</t>
         </is>
       </c>
-      <c r="HF2" s="7" t="inlineStr">
+      <c r="HF2" s="3" t="inlineStr">
         <is>
           <t>PM9 - Servitudes relatives aux zones de danger</t>
         </is>
       </c>
-      <c r="HG2" s="7" t="inlineStr">
+      <c r="HG2" s="3" t="inlineStr">
         <is>
           <t>I1 - Servitude relative à la maîtrise de l’urbanisation autour des canalisations de transport de gaz naturel ou assimilé, d’hydrocarbures et de produits chimiques et de certaines canalisations de distribution de gaz</t>
         </is>
       </c>
-      <c r="HH2" s="7" t="inlineStr">
+      <c r="HH2" s="3" t="inlineStr">
         <is>
           <t>I7 - Servitude relative à la protection des stockages souterrains de gaz naturel, d'hydrocarbures liquides, liquéfiées ou gazeux, d'hydrogène ou de produits chimiques à destination industrielle ou énergétique</t>
         </is>
       </c>
-      <c r="HI2" s="7" t="inlineStr">
+      <c r="HI2" s="3" t="inlineStr">
         <is>
           <t>I10 - Servitudes relatives à la sécurité et la prévention des risques miniers</t>
         </is>
       </c>
-      <c r="HJ2" s="7" t="inlineStr">
+      <c r="HJ2" s="3" t="inlineStr">
         <is>
           <t>Périmètre de SCOT arrêté</t>
         </is>
       </c>
-      <c r="HK2" s="7" t="inlineStr">
+      <c r="HK2" s="3" t="inlineStr">
         <is>
           <t>Schéma de cohérence territorial (non publié)</t>
         </is>
       </c>
-      <c r="HL2" s="7" t="inlineStr">
+      <c r="HL2" s="3" t="inlineStr">
         <is>
           <t>Schéma de cohérence territorial (publié)</t>
         </is>
       </c>
-      <c r="HN2" s="9" t="inlineStr">
+      <c r="HN2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Exposition Forte</t>
         </is>
       </c>
-      <c r="HO2" s="10" t="inlineStr">
+      <c r="HO2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Exposition Moayen</t>
         </is>
       </c>
-      <c r="HP2" s="11" t="inlineStr">
+      <c r="HP2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Exposition Faible</t>
         </is>
       </c>
-      <c r="HQ2" s="12" t="inlineStr">
+      <c r="HQ2" s="8" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="HR2" s="12" t="inlineStr">
+      <c r="HR2" s="8" t="inlineStr">
         <is>
           <t>Zone d'avalanches</t>
         </is>
       </c>
-      <c r="HS2" s="12" t="inlineStr">
+      <c r="HS2" s="8" t="inlineStr">
         <is>
           <t>Zone présumée avalancheuse</t>
         </is>
       </c>
-      <c r="HT2" s="12" t="inlineStr">
+      <c r="HT2" s="8" t="inlineStr">
         <is>
           <t>Dégâts importants dus au souffle</t>
         </is>
       </c>
-      <c r="HU2" s="12" t="inlineStr">
+      <c r="HU2" s="8" t="inlineStr">
         <is>
           <t>Avalanche localisée</t>
         </is>
       </c>
-      <c r="HV2" s="12" t="inlineStr">
+      <c r="HV2" s="8" t="inlineStr">
         <is>
           <t>Avalanche localisée présumée</t>
         </is>
       </c>
-      <c r="HW2" s="12" t="inlineStr">
+      <c r="HW2" s="8" t="inlineStr">
         <is>
           <t>Liaison présumée entre avalanches</t>
         </is>
       </c>
-      <c r="HX2" s="13" t="inlineStr">
+      <c r="HX2" s="9" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="HY2" s="13" t="inlineStr">
+      <c r="HY2" s="9" t="inlineStr">
         <is>
           <t>Zone d'avalanches</t>
         </is>
       </c>
-      <c r="HZ2" s="13" t="inlineStr">
+      <c r="HZ2" s="9" t="inlineStr">
         <is>
           <t>Zone présumée avalancheuse</t>
         </is>
       </c>
-      <c r="IA2" s="13" t="inlineStr">
+      <c r="IA2" s="9" t="inlineStr">
         <is>
           <t>Dégâts importants dus au souffle</t>
         </is>
       </c>
-      <c r="IB2" s="13" t="inlineStr">
+      <c r="IB2" s="9" t="inlineStr">
         <is>
           <t>Avalanche localisée</t>
         </is>
       </c>
-      <c r="IC2" s="13" t="inlineStr">
+      <c r="IC2" s="9" t="inlineStr">
         <is>
           <t>Avalanche localisée présumée</t>
         </is>
       </c>
-      <c r="ID2" s="13" t="inlineStr">
+      <c r="ID2" s="9" t="inlineStr">
         <is>
           <t>Liaison présumée entre avalanches</t>
         </is>
       </c>
-      <c r="IE2" s="14" t="inlineStr">
+      <c r="IE2" s="10" t="inlineStr">
         <is>
           <t>Zones sans 
 enquête terrain</t>
         </is>
       </c>
-      <c r="IF2" s="15" t="inlineStr">
+      <c r="IF2" s="11" t="inlineStr">
         <is>
           <t>Cave</t>
         </is>
       </c>
-      <c r="IG2" s="16" t="inlineStr">
+      <c r="IG2" s="12" t="inlineStr">
         <is>
           <t>Carrière</t>
         </is>
       </c>
-      <c r="IH2" s="17" t="inlineStr">
+      <c r="IH2" s="13" t="inlineStr">
         <is>
           <t>Naturelle</t>
         </is>
       </c>
-      <c r="II2" s="18" t="inlineStr">
+      <c r="II2" s="14" t="inlineStr">
         <is>
           <t>Indéterminée</t>
         </is>
       </c>
-      <c r="IJ2" s="19" t="inlineStr">
+      <c r="IJ2" s="15" t="inlineStr">
         <is>
           <t>Galerie</t>
         </is>
       </c>
-      <c r="IK2" s="20" t="inlineStr">
+      <c r="IK2" s="16" t="inlineStr">
         <is>
           <t>Ouvrage Civil</t>
         </is>
       </c>
-      <c r="IL2" s="21" t="inlineStr">
+      <c r="IL2" s="17" t="inlineStr">
         <is>
           <t>Ouvrage militaire</t>
         </is>
       </c>
-      <c r="IM2" s="22" t="inlineStr">
+      <c r="IM2" s="18" t="inlineStr">
         <is>
           <t>Puits</t>
         </is>
       </c>
-      <c r="IN2" s="23" t="inlineStr">
+      <c r="IN2" s="19" t="inlineStr">
         <is>
           <t>Souterrain</t>
         </is>
       </c>
-      <c r="IO2" s="24" t="inlineStr">
+      <c r="IO2" s="20" t="inlineStr">
         <is>
           <t>Communes avec cavités non localisées</t>
         </is>
       </c>
-      <c r="IP2" s="25" t="inlineStr">
+      <c r="IP2" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">
 (Zonage informatif des obligation légales de debroussaillement </t>
         </is>
       </c>
-      <c r="IQ2" s="18" t="inlineStr">
+      <c r="IQ2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="IR2" s="26" t="inlineStr">
+      <c r="IR2" s="22" t="inlineStr">
         <is>
           <t>Ouvrage de protection</t>
         </is>
       </c>
-      <c r="IS2" s="18" t="inlineStr">
+      <c r="IS2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="IT2" s="26" t="inlineStr">
+      <c r="IT2" s="22" t="inlineStr">
         <is>
           <t>Zones de sur-aléa inondation</t>
         </is>
       </c>
-      <c r="IU2" s="18" t="inlineStr">
+      <c r="IU2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="IV2" s="27" t="inlineStr">
+      <c r="IV2" s="23" t="inlineStr">
         <is>
           <t>Zone soustraittes à l'aléa Inondation)</t>
         </is>
       </c>
-      <c r="IW2" s="18" t="inlineStr">
+      <c r="IW2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="IX2" s="28" t="inlineStr">
+      <c r="IX2" s="24" t="inlineStr">
         <is>
           <t>Crue de forte probabilité</t>
         </is>
       </c>
-      <c r="IY2" s="18" t="inlineStr">
+      <c r="IY2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="IZ2" s="28" t="inlineStr">
+      <c r="IZ2" s="24" t="inlineStr">
         <is>
           <t>Crue de moyenne probabilité</t>
         </is>
       </c>
-      <c r="JA2" s="18" t="inlineStr">
+      <c r="JA2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JB2" s="28" t="inlineStr">
+      <c r="JB2" s="24" t="inlineStr">
         <is>
           <t>Crue de forte probabilité</t>
         </is>
       </c>
-      <c r="JC2" s="18" t="inlineStr">
+      <c r="JC2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JD2" s="28" t="inlineStr">
+      <c r="JD2" s="24" t="inlineStr">
         <is>
           <t>Crue de forte probabilité</t>
         </is>
       </c>
-      <c r="JE2" s="18" t="inlineStr">
+      <c r="JE2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JF2" s="28" t="inlineStr">
+      <c r="JF2" s="24" t="inlineStr">
         <is>
           <t>Crue de moyenne probabilité</t>
         </is>
       </c>
-      <c r="JG2" s="18" t="inlineStr">
+      <c r="JG2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JH2" s="28" t="inlineStr">
+      <c r="JH2" s="24" t="inlineStr">
         <is>
           <t>Evènement de moyenne probabilité avec prise en compte du changement climatique</t>
         </is>
       </c>
-      <c r="JI2" s="18" t="inlineStr">
+      <c r="JI2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JJ2" s="28" t="inlineStr">
+      <c r="JJ2" s="24" t="inlineStr">
         <is>
           <t>Crue de faible probabilité</t>
         </is>
       </c>
-      <c r="JK2" s="18" t="inlineStr">
+      <c r="JK2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JL2" s="28" t="inlineStr">
+      <c r="JL2" s="24" t="inlineStr">
         <is>
           <t>Crue de forte probabilité</t>
         </is>
       </c>
-      <c r="JM2" s="18" t="inlineStr">
+      <c r="JM2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JN2" s="28" t="inlineStr">
+      <c r="JN2" s="24" t="inlineStr">
         <is>
           <t>Crue de faible probabilité</t>
         </is>
       </c>
-      <c r="JO2" s="18" t="inlineStr">
+      <c r="JO2" s="14" t="inlineStr">
         <is>
           <t>Perimètre de TRI</t>
         </is>
       </c>
-      <c r="JP2" s="29" t="inlineStr">
+      <c r="JP2" s="25" t="inlineStr">
         <is>
           <t>Remontée de nappes
 (Entités hydrogéologiques imperméables à l'affleurement)</t>
         </is>
       </c>
-      <c r="JQ2" s="29" t="inlineStr">
+      <c r="JQ2" s="25" t="inlineStr">
         <is>
           <t>Remontée de nappes
 (Enveloppes Approchées des Innondations Potentielles en cours d'eau et submersion marine de plus d'un hectare)</t>
         </is>
       </c>
-      <c r="JR2" s="29" t="inlineStr">
+      <c r="JR2" s="25" t="inlineStr">
         <is>
           <t>Remontée de nappes
 (Masque étude spécifique en cours)</t>
         </is>
       </c>
-      <c r="JS2" s="29" t="inlineStr">
+      <c r="JS2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Zones potentiellement sujettes aux débordements de nappe fiabilité FORTE</t>
         </is>
       </c>
-      <c r="JT2" s="29" t="inlineStr">
+      <c r="JT2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Zones potentiellement sujettes aux débordements de nappe fiabilité MOYENNE</t>
         </is>
       </c>
-      <c r="JU2" s="29" t="inlineStr">
+      <c r="JU2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Zones potentiellement sujettes aux débordements de nappe fiabilité FAIBLE</t>
         </is>
       </c>
-      <c r="JV2" s="29" t="inlineStr">
+      <c r="JV2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">
 (Zones potentiellement sujettes aux débordements de nappe fiabilité INCONNUE)</t>
         </is>
       </c>
-      <c r="JW2" s="29" t="inlineStr">
+      <c r="JW2" s="25" t="inlineStr">
         <is>
           <t>Zones potentiellement sujettes aux inondations de cave fiabilité FORTE</t>
         </is>
       </c>
-      <c r="JX2" s="29" t="inlineStr">
+      <c r="JX2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Zones potentiellement sujettes aux inondations de cave fiabilité MOYENNE</t>
         </is>
       </c>
-      <c r="JY2" s="29" t="inlineStr">
+      <c r="JY2" s="25" t="inlineStr">
         <is>
           <t>Zones potentiellement sujettes aux inondations de cave fiabilité FAIBLE</t>
         </is>
       </c>
-      <c r="JZ2" s="29" t="inlineStr">
+      <c r="JZ2" s="25" t="inlineStr">
         <is>
           <t>Zones potentiellement sujettes aux inondations de cave fiabilité INCONNUE</t>
         </is>
       </c>
-      <c r="KA2" s="29" t="inlineStr">
+      <c r="KA2" s="25" t="inlineStr">
         <is>
           <t>Pas de débordement de nappe ni d'inondation de cave fiabilité FORTE</t>
         </is>
       </c>
-      <c r="KB2" s="29" t="inlineStr">
+      <c r="KB2" s="25" t="inlineStr">
         <is>
           <t>Pas de débordement de nappe ni d'inondation de cave fiabilité MOYENNE</t>
         </is>
       </c>
-      <c r="KC2" s="29" t="inlineStr">
+      <c r="KC2" s="25" t="inlineStr">
         <is>
           <t>Pas de débordement de nappe ni d'inondation de cave fiabilité FAIBLE</t>
         </is>
       </c>
-      <c r="KD2" s="29" t="inlineStr">
+      <c r="KD2" s="25" t="inlineStr">
         <is>
           <t>Pas de débordement de nappe ni d'inondation de cave fiabilité INCONNUE</t>
         </is>
       </c>
-      <c r="KE2" s="30" t="inlineStr">
+      <c r="KE2" s="26" t="inlineStr">
         <is>
           <t>Usine Seveso</t>
         </is>
       </c>
-      <c r="KF2" s="31" t="inlineStr">
+      <c r="KF2" s="27" t="inlineStr">
         <is>
           <t>Usine non Seveso</t>
         </is>
       </c>
-      <c r="KG2" s="17" t="inlineStr">
+      <c r="KG2" s="13" t="inlineStr">
         <is>
           <t>Eolienne</t>
         </is>
       </c>
-      <c r="KH2" s="32" t="inlineStr">
+      <c r="KH2" s="28" t="inlineStr">
         <is>
           <t>Elevage de bovin</t>
         </is>
       </c>
-      <c r="KI2" s="32" t="inlineStr">
+      <c r="KI2" s="28" t="inlineStr">
         <is>
           <t>Elevage de bovin</t>
         </is>
       </c>
-      <c r="KJ2" s="32" t="inlineStr">
+      <c r="KJ2" s="28" t="inlineStr">
         <is>
           <t>Elevage de volaille</t>
         </is>
       </c>
-      <c r="KK2" s="32" t="inlineStr">
+      <c r="KK2" s="28" t="inlineStr">
         <is>
           <t>Elevage de porc</t>
         </is>
       </c>
-      <c r="KL2" s="33" t="inlineStr">
+      <c r="KL2" s="29" t="inlineStr">
         <is>
           <t>Stations d'épuration</t>
         </is>
       </c>
-      <c r="KM2" s="33" t="inlineStr">
+      <c r="KM2" s="29" t="inlineStr">
         <is>
           <t>Elevage</t>
         </is>
       </c>
-      <c r="KN2" s="33" t="inlineStr">
+      <c r="KN2" s="29" t="inlineStr">
         <is>
           <t>Industries</t>
         </is>
       </c>
-      <c r="KO2" s="34" t="inlineStr">
+      <c r="KO2" s="30" t="inlineStr">
         <is>
           <t>Autres activités industrielles</t>
         </is>
       </c>
-      <c r="KP2" s="34" t="inlineStr">
+      <c r="KP2" s="30" t="inlineStr">
         <is>
           <t>Démantèlement</t>
         </is>
       </c>
-      <c r="KQ2" s="35" t="inlineStr">
+      <c r="KQ2" s="31" t="inlineStr">
         <is>
           <t>Démantèlement avec risque iode</t>
         </is>
       </c>
-      <c r="KR2" s="34" t="inlineStr">
+      <c r="KR2" s="30" t="inlineStr">
         <is>
           <t>Activités de recherche</t>
         </is>
       </c>
-      <c r="KS2" s="35" t="inlineStr">
+      <c r="KS2" s="31" t="inlineStr">
         <is>
           <t>Activités de recherche avec risque iode</t>
         </is>
       </c>
-      <c r="KT2" s="34" t="inlineStr">
+      <c r="KT2" s="30" t="inlineStr">
         <is>
           <t>Cycle du combustible</t>
         </is>
       </c>
-      <c r="KU2" s="35" t="inlineStr">
+      <c r="KU2" s="31" t="inlineStr">
         <is>
           <t>Cycle du combustible avec risque iode</t>
         </is>
       </c>
-      <c r="KV2" s="34" t="inlineStr">
+      <c r="KV2" s="30" t="inlineStr">
         <is>
           <t>Gestion des déchets radioactifs</t>
         </is>
       </c>
-      <c r="KW2" s="35" t="inlineStr">
+      <c r="KW2" s="31" t="inlineStr">
         <is>
           <t>Gestion des déchets radioactifs avec risque iode</t>
         </is>
       </c>
-      <c r="KX2" s="34" t="inlineStr">
+      <c r="KX2" s="30" t="inlineStr">
         <is>
           <t>Centrale nucléaire de production d'électricité</t>
         </is>
       </c>
-      <c r="KY2" s="35" t="inlineStr">
+      <c r="KY2" s="31" t="inlineStr">
         <is>
           <t>Centrale nucléaire de production d'électricité avec risque iode</t>
         </is>
       </c>
-      <c r="KZ2" s="36" t="inlineStr">
+      <c r="KZ2" s="32" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en instruction</t>
         </is>
       </c>
-      <c r="LA2" s="35" t="inlineStr">
+      <c r="LA2" s="31" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en attente de construction</t>
         </is>
       </c>
-      <c r="LB2" s="37" t="inlineStr">
+      <c r="LB2" s="33" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en construction</t>
         </is>
       </c>
-      <c r="LC2" s="24" t="inlineStr">
+      <c r="LC2" s="20" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en exploitation</t>
         </is>
       </c>
-      <c r="LD2" s="38" t="inlineStr">
+      <c r="LD2" s="34" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en cessation d'activité</t>
         </is>
       </c>
-      <c r="LE2" s="39" t="inlineStr">
+      <c r="LE2" s="35" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en instruction</t>
         </is>
       </c>
-      <c r="LF2" s="37" t="inlineStr">
+      <c r="LF2" s="33" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en attente de construction</t>
         </is>
       </c>
-      <c r="LG2" s="40" t="inlineStr">
+      <c r="LG2" s="36" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en construction</t>
         </is>
       </c>
-      <c r="LH2" s="24" t="inlineStr">
+      <c r="LH2" s="20" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en exploitation</t>
         </is>
       </c>
-      <c r="LI2" s="38" t="inlineStr">
+      <c r="LI2" s="34" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en cessation d'activité</t>
         </is>
       </c>
-      <c r="LJ2" s="41" t="inlineStr">
+      <c r="LJ2" s="37" t="inlineStr">
         <is>
           <t>Parcs éoliens terrestres en instruction</t>
         </is>
       </c>
-      <c r="LK2" s="13" t="inlineStr">
+      <c r="LK2" s="9" t="inlineStr">
         <is>
           <t>Parcs éoliens terrestres en attente de construction</t>
         </is>
       </c>
-      <c r="LL2" s="42" t="inlineStr">
+      <c r="LL2" s="38" t="inlineStr">
         <is>
           <t>Parcs éoliens terrestres en construction</t>
         </is>
       </c>
-      <c r="LM2" s="43" t="inlineStr">
+      <c r="LM2" s="39" t="inlineStr">
         <is>
           <t>Parcs éoliens terrestres en exploitation</t>
         </is>
       </c>
-      <c r="LN2" s="38" t="inlineStr">
+      <c r="LN2" s="34" t="inlineStr">
         <is>
           <t>Parcs éoliens terrestres en cessation d'activité</t>
         </is>
       </c>
-      <c r="LO2" s="39" t="inlineStr">
+      <c r="LO2" s="35" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en instruction</t>
         </is>
       </c>
-      <c r="LP2" s="37" t="inlineStr">
+      <c r="LP2" s="33" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en attente de construction</t>
         </is>
       </c>
-      <c r="LQ2" s="40" t="inlineStr">
+      <c r="LQ2" s="36" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en construction</t>
         </is>
       </c>
-      <c r="LR2" s="24" t="inlineStr">
+      <c r="LR2" s="20" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en exploitation</t>
         </is>
       </c>
-      <c r="LS2" s="38" t="inlineStr">
+      <c r="LS2" s="34" t="inlineStr">
         <is>
           <t>Eoliennes appartenant à un parc en cessation d'activité</t>
         </is>
       </c>
-      <c r="LT2" s="44" t="inlineStr">
+      <c r="LT2" s="40" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en instruction</t>
         </is>
       </c>
-      <c r="LU2" s="45" t="inlineStr">
+      <c r="LU2" s="41" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en attente de construction</t>
         </is>
       </c>
-      <c r="LV2" s="46" t="inlineStr">
+      <c r="LV2" s="42" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en construction</t>
         </is>
       </c>
-      <c r="LW2" s="47" t="inlineStr">
+      <c r="LW2" s="43" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en exploitation</t>
         </is>
       </c>
-      <c r="LX2" s="48" t="inlineStr">
+      <c r="LX2" s="44" t="inlineStr">
         <is>
           <t>Postes de livraison appartenant à un parc en cessation d'activité</t>
         </is>
       </c>
-      <c r="LY2" s="18" t="inlineStr">
+      <c r="LY2" s="14" t="inlineStr">
         <is>
           <t>Glissement</t>
         </is>
       </c>
-      <c r="LZ2" s="32" t="inlineStr">
+      <c r="LZ2" s="28" t="inlineStr">
         <is>
           <t>Eboulement</t>
         </is>
       </c>
-      <c r="MA2" s="17" t="inlineStr">
+      <c r="MA2" s="13" t="inlineStr">
         <is>
           <t>Coulee</t>
         </is>
       </c>
-      <c r="MB2" s="49" t="inlineStr">
+      <c r="MB2" s="45" t="inlineStr">
         <is>
           <t>Effondrement</t>
         </is>
       </c>
-      <c r="MC2" s="50" t="inlineStr">
+      <c r="MC2" s="46" t="inlineStr">
         <is>
           <t>Erosion des berges</t>
         </is>
       </c>
-      <c r="MD2" s="51" t="inlineStr">
+      <c r="MD2" s="47" t="inlineStr">
         <is>
           <t>Mouvements des terrain non localiés</t>
         </is>
       </c>
-      <c r="ME2" s="52" t="inlineStr">
+      <c r="ME2" s="48" t="inlineStr">
         <is>
           <t>PPR INONDATION
 Périmètre -PPRN Risque Inondation</t>
         </is>
       </c>
-      <c r="MF2" s="51" t="inlineStr">
+      <c r="MF2" s="47" t="inlineStr">
         <is>
           <t>PPR LITTORAUX
 Périmètre -PPRN Risque Inondation- Par sublension marine</t>
         </is>
       </c>
-      <c r="MG2" s="53" t="inlineStr">
+      <c r="MG2" s="49" t="inlineStr">
         <is>
           <t>PPR Mouvement de terrain
 Périmètre- PPRN Risque Mouvement de terrain</t>
         </is>
       </c>
-      <c r="MH2" s="54" t="inlineStr">
+      <c r="MH2" s="50" t="inlineStr">
         <is>
           <t>PPR Feu de forêt
 Périmètre-PPRN Risque Avalanche</t>
         </is>
       </c>
-      <c r="MI2" s="55" t="inlineStr">
+      <c r="MI2" s="51" t="inlineStr">
         <is>
           <t>PPR Avalanche
 PPRN Risque Avalanche</t>
         </is>
       </c>
-      <c r="MJ2" s="56" t="inlineStr">
+      <c r="MJ2" s="83" t="inlineStr">
         <is>
           <t>PPR Seisme
 PPRN Risque Seisme</t>
         </is>
       </c>
-      <c r="MK2" s="57" t="inlineStr">
+      <c r="MK2" s="53" t="inlineStr">
         <is>
           <t>PPR Risque Minier
 PPRT Risque Minier</t>
         </is>
       </c>
-      <c r="ML2" s="58" t="inlineStr">
+      <c r="ML2" s="54" t="inlineStr">
         <is>
           <t>PPR Risque Industriel
 PPRT Risque Industriel</t>
         </is>
       </c>
-      <c r="MM2" s="39" t="inlineStr">
+      <c r="MM2" s="35" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Inondation prescrit</t>
         </is>
       </c>
-      <c r="MN2" s="59" t="inlineStr">
+      <c r="MN2" s="55" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Inondation approuvé</t>
         </is>
       </c>
-      <c r="MO2" s="60" t="inlineStr">
+      <c r="MO2" s="56" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Inondation par submersion marine prescrit</t>
         </is>
       </c>
-      <c r="MP2" s="59" t="inlineStr">
+      <c r="MP2" s="55" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Inondation par submersion marine approuvé</t>
         </is>
       </c>
-      <c r="MQ2" s="61" t="inlineStr">
+      <c r="MQ2" s="57" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Mouvement de terrain prescrit</t>
         </is>
       </c>
-      <c r="MR2" s="62" t="inlineStr">
+      <c r="MR2" s="58" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Mouvement de terrain approuvé</t>
         </is>
       </c>
-      <c r="MS2" s="63" t="inlineStr">
+      <c r="MS2" s="59" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Mouvement de terrain - Affaissements et effondrements (Cavités souterraines) prescrit</t>
         </is>
       </c>
-      <c r="MT2" s="64" t="inlineStr">
+      <c r="MT2" s="60" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Mouvement de terrain - Affaissements et effondrements (Cavités souterraines) approuvé</t>
         </is>
       </c>
-      <c r="MU2" s="63" t="inlineStr">
+      <c r="MU2" s="59" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Mouvement de terrain - Tassements différentiels (Argile) prescrit</t>
         </is>
       </c>
-      <c r="MV2" s="64" t="inlineStr">
+      <c r="MV2" s="60" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Mouvement de terrain - Tassements différentiels (Argile) approuvé</t>
         </is>
       </c>
-      <c r="MW2" s="65" t="inlineStr">
+      <c r="MW2" s="61" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Feu de forêt prescrit</t>
         </is>
       </c>
-      <c r="MX2" s="66" t="inlineStr">
+      <c r="MX2" s="62" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Feu de forêt approuvé</t>
         </is>
       </c>
-      <c r="MY2" s="39" t="inlineStr">
+      <c r="MY2" s="35" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Avalanche prescrit</t>
         </is>
       </c>
-      <c r="MZ2" s="52" t="inlineStr">
+      <c r="MZ2" s="48" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Avalanche approuvé</t>
         </is>
       </c>
-      <c r="NA2" s="67" t="inlineStr">
+      <c r="NA2" s="63" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Séisme prescrit</t>
         </is>
       </c>
-      <c r="NB2" s="40" t="inlineStr">
+      <c r="NB2" s="36" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Séisme approuvé</t>
         </is>
       </c>
-      <c r="NC2" s="68" t="inlineStr">
+      <c r="NC2" s="64" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Éruption volcanique prescrit</t>
         </is>
       </c>
-      <c r="ND2" s="69" t="inlineStr">
+      <c r="ND2" s="65" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Éruption volcanique approuvé</t>
         </is>
       </c>
-      <c r="NE2" s="39" t="inlineStr">
+      <c r="NE2" s="35" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Phénomènes météorologiques prescrit</t>
         </is>
       </c>
-      <c r="NF2" s="27" t="inlineStr">
+      <c r="NF2" s="23" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque Phénomènes météorologiques approuvé</t>
         </is>
       </c>
-      <c r="NG2" s="61" t="inlineStr">
+      <c r="NG2" s="57" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque industriel prescrit</t>
         </is>
       </c>
-      <c r="NH2" s="62" t="inlineStr">
+      <c r="NH2" s="58" t="inlineStr">
         <is>
           <t>Commune concernée par un PPRN Risque industriel approuvé</t>
         </is>
       </c>
-      <c r="NI2" s="39" t="inlineStr">
+      <c r="NI2" s="35" t="inlineStr">
         <is>
           <t>Zone à risque d'inondation entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NJ2" s="12" t="inlineStr">
+      <c r="NJ2" s="8" t="inlineStr">
         <is>
           <t>Zone à risque de mouvement de terrain entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NK2" s="62" t="inlineStr">
+      <c r="NK2" s="58" t="inlineStr">
         <is>
           <t>Zone à risque d'incendie entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NL2" s="38" t="inlineStr">
+      <c r="NL2" s="34" t="inlineStr">
         <is>
           <t>Zone à risque d'avalanche entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NM2" s="70" t="inlineStr">
+      <c r="NM2" s="66" t="inlineStr">
         <is>
           <t>Zone à risque minier entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NN2" s="38" t="inlineStr">
+      <c r="NN2" s="34" t="inlineStr">
         <is>
           <t>Zone à risque volcanique entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NO2" s="38" t="inlineStr">
+      <c r="NO2" s="34" t="inlineStr">
         <is>
           <t>Zone à risque cyclonique entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NP2" s="71" t="inlineStr">
+      <c r="NP2" s="67" t="inlineStr">
         <is>
           <t>Zone à risque industriel entraînant une servitude d'utilité publique</t>
         </is>
       </c>
-      <c r="NQ2" s="72" t="inlineStr">
+      <c r="NQ2" s="68" t="inlineStr">
         <is>
           <t>Catégorie 1</t>
         </is>
       </c>
-      <c r="NR2" s="73" t="inlineStr">
+      <c r="NR2" s="69" t="inlineStr">
         <is>
           <t>Catégorie 2</t>
         </is>
       </c>
-      <c r="NS2" s="74" t="inlineStr">
+      <c r="NS2" s="70" t="inlineStr">
         <is>
           <t>Catégorie 3</t>
         </is>
       </c>
-      <c r="NT2" s="75" t="inlineStr">
+      <c r="NT2" s="71" t="inlineStr">
         <is>
           <t>Produits Chimiques</t>
         </is>
       </c>
-      <c r="NU2" s="18" t="inlineStr">
+      <c r="NU2" s="14" t="inlineStr">
         <is>
           <t>Hydrocarbures</t>
         </is>
       </c>
-      <c r="NV2" s="31" t="inlineStr">
+      <c r="NV2" s="27" t="inlineStr">
         <is>
           <t>Gaz Naturel</t>
         </is>
       </c>
-      <c r="NW2" s="76" t="inlineStr">
+      <c r="NW2" s="72" t="inlineStr">
         <is>
           <t>Localisation des anciens sites industriels et activités de service</t>
         </is>
       </c>
-      <c r="NX2" s="76" t="inlineStr">
+      <c r="NX2" s="72" t="inlineStr">
         <is>
           <t>Emprises des anciens sites industriels et activités de service</t>
         </is>
       </c>
-      <c r="NY2" s="18" t="inlineStr">
+      <c r="NY2" s="14" t="inlineStr">
         <is>
           <t>ocalisations des sites industriels</t>
         </is>
       </c>
-      <c r="NZ2" s="18" t="inlineStr">
+      <c r="NZ2" s="14" t="inlineStr">
         <is>
           <t>Emprises des sites industriels</t>
         </is>
       </c>
-      <c r="OA2" s="61" t="inlineStr">
+      <c r="OA2" s="57" t="inlineStr">
         <is>
           <t>Emprises des secteurs d'information sur les sols</t>
         </is>
       </c>
-      <c r="OB2" s="62" t="inlineStr">
+      <c r="OB2" s="58" t="inlineStr">
         <is>
           <t>Emprises des servitudes d'utilité publique</t>
         </is>
       </c>
-      <c r="OC2" s="8" t="inlineStr">
+      <c r="OC2" s="4" t="inlineStr">
         <is>
           <t>Sismicité très faible</t>
         </is>
       </c>
-      <c r="OD2" s="37" t="inlineStr">
+      <c r="OD2" s="33" t="inlineStr">
         <is>
           <t>Sismicité  faible</t>
         </is>
       </c>
-      <c r="OE2" s="77" t="inlineStr">
+      <c r="OE2" s="73" t="inlineStr">
         <is>
           <t>Sismicité modorée</t>
         </is>
       </c>
-      <c r="OF2" s="78" t="inlineStr">
+      <c r="OF2" s="74" t="inlineStr">
         <is>
           <t>Sismicité moyenne</t>
         </is>
       </c>
-      <c r="OG2" s="79" t="inlineStr">
+      <c r="OG2" s="75" t="inlineStr">
         <is>
           <t>Sismicité forte</t>
         </is>
       </c>
-      <c r="OH2" s="80" t="inlineStr">
+      <c r="OH2" s="76" t="inlineStr">
         <is>
           <t>IIIUBb</t>
         </is>
       </c>
-      <c r="OI2" s="80" t="inlineStr">
+      <c r="OI2" s="76" t="inlineStr">
         <is>
           <t>IIIUE</t>
         </is>
       </c>
-      <c r="OJ2" s="80" t="inlineStr">
+      <c r="OJ2" s="76" t="inlineStr">
         <is>
           <t>IIIUE</t>
         </is>
       </c>
-      <c r="OK2" s="80" t="inlineStr">
+      <c r="OK2" s="76" t="inlineStr">
         <is>
           <t>IIIUEa</t>
         </is>
       </c>
-      <c r="OL2" s="80" t="inlineStr">
+      <c r="OL2" s="76" t="inlineStr">
         <is>
           <t>IIUA</t>
         </is>
       </c>
-      <c r="OM2" s="80" t="inlineStr">
+      <c r="OM2" s="76" t="inlineStr">
         <is>
           <t>IIUE</t>
         </is>
       </c>
-      <c r="ON2" s="80" t="inlineStr">
+      <c r="ON2" s="76" t="inlineStr">
         <is>
           <t>IIUE</t>
         </is>
       </c>
-      <c r="OO2" s="80" t="inlineStr">
+      <c r="OO2" s="76" t="inlineStr">
         <is>
           <t>IVUB</t>
         </is>
       </c>
-      <c r="OP2" s="80" t="inlineStr">
+      <c r="OP2" s="76" t="inlineStr">
         <is>
           <t>SPR</t>
         </is>
       </c>
-      <c r="OQ2" s="80" t="inlineStr">
+      <c r="OQ2" s="76" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="OR2" s="80" t="inlineStr">
+      <c r="OR2" s="76" t="inlineStr">
         <is>
           <t>U1</t>
         </is>
       </c>
-      <c r="OS2" s="80" t="inlineStr">
+      <c r="OS2" s="76" t="inlineStr">
         <is>
           <t>U2</t>
         </is>
       </c>
-      <c r="OT2" s="80" t="inlineStr">
+      <c r="OT2" s="76" t="inlineStr">
         <is>
           <t>U3</t>
         </is>
       </c>
-      <c r="OU2" s="80" t="inlineStr">
+      <c r="OU2" s="76" t="inlineStr">
         <is>
           <t>U4</t>
         </is>
       </c>
-      <c r="OV2" s="80" t="inlineStr">
+      <c r="OV2" s="76" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="OW2" s="80" t="inlineStr">
+      <c r="OW2" s="76" t="inlineStr">
         <is>
           <t>Ua1</t>
         </is>
       </c>
-      <c r="OX2" s="80" t="inlineStr">
+      <c r="OX2" s="76" t="inlineStr">
         <is>
           <t>Ua2</t>
         </is>
       </c>
-      <c r="OY2" s="80" t="inlineStr">
+      <c r="OY2" s="76" t="inlineStr">
         <is>
           <t>UA3</t>
         </is>
       </c>
-      <c r="OZ2" s="80" t="inlineStr">
+      <c r="OZ2" s="76" t="inlineStr">
         <is>
           <t>UA-2+</t>
         </is>
       </c>
-      <c r="PA2" s="80" t="inlineStr">
+      <c r="PA2" s="76" t="inlineStr">
         <is>
           <t>Uaa</t>
         </is>
       </c>
-      <c r="PB2" s="80" t="inlineStr">
+      <c r="PB2" s="76" t="inlineStr">
         <is>
           <t>UAb</t>
         </is>
       </c>
-      <c r="PC2" s="80" t="inlineStr">
+      <c r="PC2" s="76" t="inlineStr">
         <is>
           <t>UAj</t>
         </is>
       </c>
-      <c r="PD2" s="80" t="inlineStr">
+      <c r="PD2" s="76" t="inlineStr">
         <is>
           <t>UAp</t>
         </is>
       </c>
-      <c r="PE2" s="80" t="inlineStr">
+      <c r="PE2" s="76" t="inlineStr">
         <is>
           <t>UB</t>
         </is>
       </c>
-      <c r="PF2" s="80" t="inlineStr">
+      <c r="PF2" s="76" t="inlineStr">
         <is>
           <t>Uba</t>
         </is>
       </c>
-      <c r="PG2" s="80" t="inlineStr">
+      <c r="PG2" s="76" t="inlineStr">
         <is>
           <t>UB1-1</t>
         </is>
       </c>
-      <c r="PH2" s="80" t="inlineStr">
+      <c r="PH2" s="76" t="inlineStr">
         <is>
           <t>UB-2</t>
         </is>
       </c>
-      <c r="PI2" s="80" t="inlineStr">
+      <c r="PI2" s="76" t="inlineStr">
         <is>
           <t>UBb</t>
         </is>
       </c>
-      <c r="PJ2" s="80" t="inlineStr">
+      <c r="PJ2" s="76" t="inlineStr">
         <is>
           <t>UBc</t>
         </is>
       </c>
-      <c r="PK2" s="80" t="inlineStr">
+      <c r="PK2" s="76" t="inlineStr">
         <is>
           <t>UBd</t>
         </is>
       </c>
-      <c r="PL2" s="80" t="inlineStr">
+      <c r="PL2" s="76" t="inlineStr">
         <is>
           <t>UBh</t>
         </is>
       </c>
-      <c r="PM2" s="80" t="inlineStr">
+      <c r="PM2" s="76" t="inlineStr">
         <is>
           <t>UC</t>
         </is>
       </c>
-      <c r="PN2" s="80" t="inlineStr">
+      <c r="PN2" s="76" t="inlineStr">
         <is>
           <t>UC3</t>
         </is>
       </c>
-      <c r="PO2" s="80" t="inlineStr">
+      <c r="PO2" s="76" t="inlineStr">
         <is>
           <t>UC91Jb2</t>
         </is>
       </c>
-      <c r="PP2" s="80" t="inlineStr">
+      <c r="PP2" s="76" t="inlineStr">
         <is>
           <t>UCa</t>
         </is>
       </c>
-      <c r="PQ2" s="80" t="inlineStr">
+      <c r="PQ2" s="76" t="inlineStr">
         <is>
           <t>UCr</t>
         </is>
       </c>
-      <c r="PR2" s="80" t="inlineStr">
+      <c r="PR2" s="76" t="inlineStr">
         <is>
           <t>Uc3c</t>
         </is>
       </c>
-      <c r="PS2" s="80" t="inlineStr">
+      <c r="PS2" s="76" t="inlineStr">
         <is>
           <t>UD</t>
         </is>
       </c>
-      <c r="PT2" s="80" t="inlineStr">
+      <c r="PT2" s="76" t="inlineStr">
         <is>
           <t>UD1</t>
         </is>
       </c>
-      <c r="PU2" s="80" t="inlineStr">
+      <c r="PU2" s="76" t="inlineStr">
         <is>
           <t>UDP</t>
         </is>
       </c>
-      <c r="PV2" s="80" t="inlineStr">
+      <c r="PV2" s="76" t="inlineStr">
         <is>
           <t>UE</t>
         </is>
       </c>
-      <c r="PW2" s="80" t="inlineStr">
+      <c r="PW2" s="76" t="inlineStr">
         <is>
           <t>UE(P2)</t>
         </is>
       </c>
-      <c r="PX2" s="80" t="inlineStr">
+      <c r="PX2" s="76" t="inlineStr">
         <is>
           <t>UE(P3)</t>
         </is>
       </c>
-      <c r="PY2" s="80" t="inlineStr">
+      <c r="PY2" s="76" t="inlineStr">
         <is>
           <t>UEa</t>
         </is>
       </c>
-      <c r="PZ2" s="80" t="inlineStr">
+      <c r="PZ2" s="76" t="inlineStr">
         <is>
           <t>UEc</t>
         </is>
       </c>
-      <c r="QA2" s="80" t="inlineStr">
+      <c r="QA2" s="76" t="inlineStr">
         <is>
           <t>Uef</t>
         </is>
       </c>
-      <c r="QB2" s="80" t="inlineStr">
+      <c r="QB2" s="76" t="inlineStr">
         <is>
           <t>Uec</t>
         </is>
       </c>
-      <c r="QC2" s="80" t="inlineStr">
+      <c r="QC2" s="76" t="inlineStr">
         <is>
           <t>UEi</t>
         </is>
       </c>
-      <c r="QD2" s="80" t="inlineStr">
+      <c r="QD2" s="76" t="inlineStr">
         <is>
           <t>UEie</t>
         </is>
       </c>
-      <c r="QE2" s="80" t="inlineStr">
+      <c r="QE2" s="76" t="inlineStr">
         <is>
           <t>UEm</t>
         </is>
       </c>
-      <c r="QF2" s="80" t="inlineStr">
+      <c r="QF2" s="76" t="inlineStr">
         <is>
           <t>Uep</t>
         </is>
       </c>
-      <c r="QG2" s="80" t="inlineStr">
+      <c r="QG2" s="76" t="inlineStr">
         <is>
           <t>UES</t>
         </is>
       </c>
-      <c r="QH2" s="80" t="inlineStr">
+      <c r="QH2" s="76" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
       </c>
-      <c r="QI2" s="80" t="inlineStr">
+      <c r="QI2" s="76" t="inlineStr">
         <is>
           <t>UGa1</t>
         </is>
       </c>
-      <c r="QJ2" s="80" t="inlineStr">
+      <c r="QJ2" s="76" t="inlineStr">
         <is>
           <t>UGa2</t>
         </is>
       </c>
-      <c r="QK2" s="80" t="inlineStr">
+      <c r="QK2" s="76" t="inlineStr">
         <is>
           <t>UGb</t>
         </is>
       </c>
-      <c r="QL2" s="80" t="inlineStr">
+      <c r="QL2" s="76" t="inlineStr">
         <is>
           <t>UGc</t>
         </is>
       </c>
-      <c r="QM2" s="80" t="inlineStr">
+      <c r="QM2" s="76" t="inlineStr">
         <is>
           <t>UH</t>
         </is>
       </c>
-      <c r="QN2" s="80" t="inlineStr">
+      <c r="QN2" s="76" t="inlineStr">
         <is>
           <t>Uhc2</t>
         </is>
       </c>
-      <c r="QO2" s="80" t="inlineStr">
+      <c r="QO2" s="76" t="inlineStr">
         <is>
           <t>UH1</t>
         </is>
       </c>
-      <c r="QP2" s="80" t="inlineStr">
+      <c r="QP2" s="76" t="inlineStr">
         <is>
           <t>UJ</t>
         </is>
       </c>
-      <c r="QQ2" s="80" t="inlineStr">
+      <c r="QQ2" s="76" t="inlineStr">
         <is>
           <t>ULb</t>
         </is>
       </c>
-      <c r="QR2" s="80" t="inlineStr">
+      <c r="QR2" s="76" t="inlineStr">
         <is>
           <t>UM</t>
         </is>
       </c>
-      <c r="QS2" s="80" t="inlineStr">
+      <c r="QS2" s="76" t="inlineStr">
         <is>
           <t>Uma</t>
         </is>
       </c>
-      <c r="QT2" s="80" t="inlineStr">
+      <c r="QT2" s="76" t="inlineStr">
         <is>
           <t>Umb</t>
         </is>
       </c>
-      <c r="QU2" s="80" t="inlineStr">
+      <c r="QU2" s="76" t="inlineStr">
         <is>
           <t>UNe</t>
         </is>
       </c>
-      <c r="QV2" s="80" t="inlineStr">
+      <c r="QV2" s="76" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="QW2" s="80" t="inlineStr">
+      <c r="QW2" s="76" t="inlineStr">
         <is>
           <t>UP1</t>
         </is>
       </c>
-      <c r="QX2" s="80" t="inlineStr">
+      <c r="QX2" s="76" t="inlineStr">
         <is>
           <t>UPJ</t>
         </is>
       </c>
-      <c r="QY2" s="80" t="inlineStr">
+      <c r="QY2" s="76" t="inlineStr">
         <is>
           <t>URa</t>
         </is>
       </c>
-      <c r="QZ2" s="80" t="inlineStr">
+      <c r="QZ2" s="76" t="inlineStr">
         <is>
           <t>URb</t>
         </is>
       </c>
-      <c r="RA2" s="80" t="inlineStr">
+      <c r="RA2" s="76" t="inlineStr">
         <is>
           <t>UT</t>
         </is>
       </c>
-      <c r="RB2" s="80" t="inlineStr">
+      <c r="RB2" s="76" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="RC2" s="80" t="inlineStr">
+      <c r="RC2" s="76" t="inlineStr">
         <is>
           <t>USv</t>
         </is>
       </c>
-      <c r="RD2" s="80" t="inlineStr">
+      <c r="RD2" s="76" t="inlineStr">
         <is>
           <t>USx</t>
         </is>
       </c>
-      <c r="RE2" s="80" t="inlineStr">
+      <c r="RE2" s="76" t="inlineStr">
         <is>
           <t>UV</t>
         </is>
       </c>
-      <c r="RF2" s="80" t="inlineStr">
+      <c r="RF2" s="76" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="RG2" s="80" t="inlineStr">
+      <c r="RG2" s="76" t="inlineStr">
         <is>
           <t>Uxa</t>
         </is>
       </c>
-      <c r="RH2" s="80" t="inlineStr">
+      <c r="RH2" s="76" t="inlineStr">
         <is>
           <t>UX3l</t>
         </is>
       </c>
-      <c r="RI2" s="80" t="inlineStr">
+      <c r="RI2" s="76" t="inlineStr">
         <is>
           <t>UXc</t>
         </is>
       </c>
-      <c r="RJ2" s="80" t="inlineStr">
+      <c r="RJ2" s="76" t="inlineStr">
         <is>
           <t>Uxcp</t>
         </is>
       </c>
-      <c r="RK2" s="80" t="inlineStr">
+      <c r="RK2" s="76" t="inlineStr">
         <is>
           <t>UXf</t>
         </is>
       </c>
-      <c r="RL2" s="80" t="inlineStr">
+      <c r="RL2" s="76" t="inlineStr">
         <is>
           <t>Uxi</t>
         </is>
       </c>
-      <c r="RM2" s="80" t="inlineStr">
+      <c r="RM2" s="76" t="inlineStr">
         <is>
           <t>UXm</t>
         </is>
       </c>
-      <c r="RN2" s="80" t="inlineStr">
+      <c r="RN2" s="76" t="inlineStr">
         <is>
           <t>UXt</t>
         </is>
       </c>
-      <c r="RO2" s="80" t="inlineStr">
+      <c r="RO2" s="76" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="RP2" s="80" t="inlineStr">
+      <c r="RP2" s="76" t="inlineStr">
         <is>
           <t>UYb</t>
         </is>
       </c>
-      <c r="RQ2" s="80" t="inlineStr">
+      <c r="RQ2" s="76" t="inlineStr">
         <is>
           <t>UYc</t>
         </is>
       </c>
-      <c r="RR2" s="80" t="inlineStr">
+      <c r="RR2" s="76" t="inlineStr">
         <is>
           <t>UZ</t>
         </is>
       </c>
-      <c r="RS2" s="80" t="inlineStr">
+      <c r="RS2" s="76" t="inlineStr">
         <is>
           <t>Uzoo</t>
         </is>
       </c>
-      <c r="RT2" s="80" t="inlineStr">
+      <c r="RT2" s="76" t="inlineStr">
         <is>
           <t>VIUB</t>
         </is>
       </c>
-      <c r="RU2" s="80" t="inlineStr">
+      <c r="RU2" s="76" t="inlineStr">
         <is>
           <t>VIUEb</t>
         </is>
       </c>
-      <c r="RV2" s="80" t="inlineStr">
+      <c r="RV2" s="76" t="inlineStr">
         <is>
           <t>VIUEc</t>
         </is>
       </c>
-      <c r="RW2" s="80" t="inlineStr">
+      <c r="RW2" s="76" t="inlineStr">
         <is>
           <t>VIUEd</t>
         </is>
       </c>
-      <c r="RX2" s="80" t="inlineStr">
+      <c r="RX2" s="76" t="inlineStr">
         <is>
           <t>VIUEe</t>
         </is>
       </c>
-      <c r="RY2" s="80" t="inlineStr">
+      <c r="RY2" s="76" t="inlineStr">
         <is>
           <t>VUB</t>
         </is>
       </c>
-      <c r="RZ2" s="80" t="inlineStr">
+      <c r="RZ2" s="76" t="inlineStr">
         <is>
           <t>VUB</t>
         </is>
       </c>
-      <c r="SA2" s="80" t="inlineStr">
+      <c r="SA2" s="76" t="inlineStr">
         <is>
           <t>VUBa</t>
         </is>
       </c>
-      <c r="SB2" s="80" t="inlineStr">
+      <c r="SB2" s="76" t="inlineStr">
         <is>
           <t>VUE</t>
         </is>
       </c>
-      <c r="SC2" s="80" t="inlineStr">
+      <c r="SC2" s="76" t="inlineStr">
         <is>
           <t>VUEa</t>
         </is>
       </c>
-      <c r="SD2" s="80" t="inlineStr">
+      <c r="SD2" s="76" t="inlineStr">
         <is>
           <t>VUEb</t>
         </is>
       </c>
-      <c r="SE2" s="80" t="inlineStr">
+      <c r="SE2" s="76" t="inlineStr">
         <is>
           <t>VUEd</t>
         </is>
       </c>
-      <c r="SF2" s="80" t="inlineStr">
+      <c r="SF2" s="76" t="inlineStr">
         <is>
           <t>VUEe</t>
         </is>
       </c>
-      <c r="SG2" s="80" t="inlineStr">
+      <c r="SG2" s="76" t="inlineStr">
         <is>
           <t>VUEf</t>
         </is>
       </c>
-      <c r="SH2" s="80" t="inlineStr">
+      <c r="SH2" s="76" t="inlineStr">
         <is>
           <t>VUEg</t>
         </is>
       </c>
-      <c r="SI2" s="80" t="inlineStr">
+      <c r="SI2" s="76" t="inlineStr">
         <is>
           <t>VUEh</t>
         </is>
       </c>
-      <c r="SJ2" s="81" t="inlineStr">
+      <c r="SJ2" s="77" t="inlineStr">
         <is>
           <t>1AU</t>
         </is>
       </c>
-      <c r="SK2" s="81" t="inlineStr">
+      <c r="SK2" s="77" t="inlineStr">
         <is>
           <t>1AUa</t>
         </is>
       </c>
-      <c r="SL2" s="81" t="inlineStr">
+      <c r="SL2" s="77" t="inlineStr">
         <is>
           <t>1AUc</t>
         </is>
       </c>
-      <c r="SM2" s="81" t="inlineStr">
+      <c r="SM2" s="77" t="inlineStr">
         <is>
           <t>1AUE</t>
         </is>
       </c>
-      <c r="SN2" s="81" t="inlineStr">
+      <c r="SN2" s="77" t="inlineStr">
         <is>
           <t>1AUH</t>
         </is>
       </c>
-      <c r="SO2" s="81" t="inlineStr">
+      <c r="SO2" s="77" t="inlineStr">
         <is>
           <t>1AUH1</t>
         </is>
       </c>
-      <c r="SP2" s="81" t="inlineStr">
+      <c r="SP2" s="77" t="inlineStr">
         <is>
           <t>1AUHc2</t>
         </is>
       </c>
-      <c r="SQ2" s="81" t="inlineStr">
+      <c r="SQ2" s="77" t="inlineStr">
         <is>
           <t>1AUG</t>
         </is>
       </c>
-      <c r="SR2" s="81" t="inlineStr">
+      <c r="SR2" s="77" t="inlineStr">
         <is>
           <t>1AUX</t>
         </is>
       </c>
-      <c r="SS2" s="81" t="inlineStr">
+      <c r="SS2" s="77" t="inlineStr">
         <is>
           <t>1AUXa</t>
         </is>
       </c>
-      <c r="ST2" s="81" t="inlineStr">
+      <c r="ST2" s="77" t="inlineStr">
         <is>
           <t>1AUy</t>
         </is>
       </c>
-      <c r="SU2" s="81" t="inlineStr">
+      <c r="SU2" s="77" t="inlineStr">
         <is>
           <t>2AU</t>
         </is>
       </c>
-      <c r="SV2" s="81" t="inlineStr">
+      <c r="SV2" s="77" t="inlineStr">
         <is>
           <t>AU1</t>
         </is>
       </c>
-      <c r="SW2" s="81" t="inlineStr">
+      <c r="SW2" s="77" t="inlineStr">
         <is>
           <t>AU2</t>
         </is>
       </c>
-      <c r="SX2" s="81" t="inlineStr">
+      <c r="SX2" s="77" t="inlineStr">
         <is>
           <t>AU1c</t>
         </is>
       </c>
-      <c r="SY2" s="81" t="inlineStr">
+      <c r="SY2" s="77" t="inlineStr">
         <is>
           <t>AU1Ec</t>
         </is>
       </c>
-      <c r="SZ2" s="81" t="inlineStr">
+      <c r="SZ2" s="77" t="inlineStr">
         <is>
           <t>AU1EH</t>
         </is>
       </c>
-      <c r="TA2" s="81" t="inlineStr">
+      <c r="TA2" s="77" t="inlineStr">
         <is>
           <t>AU2E1</t>
         </is>
       </c>
-      <c r="TB2" s="81" t="inlineStr">
+      <c r="TB2" s="77" t="inlineStr">
         <is>
           <t>AUD</t>
         </is>
       </c>
-      <c r="TC2" s="81" t="inlineStr">
+      <c r="TC2" s="77" t="inlineStr">
         <is>
           <t>AUE</t>
         </is>
       </c>
-      <c r="TD2" s="81" t="inlineStr">
+      <c r="TD2" s="77" t="inlineStr">
         <is>
           <t>AUH</t>
         </is>
       </c>
-      <c r="TE2" s="81" t="inlineStr">
+      <c r="TE2" s="77" t="inlineStr">
         <is>
           <t>AUL</t>
         </is>
       </c>
-      <c r="TF2" s="81" t="inlineStr">
+      <c r="TF2" s="77" t="inlineStr">
         <is>
           <t>AUPJ</t>
         </is>
       </c>
-      <c r="TG2" s="81" t="inlineStr">
+      <c r="TG2" s="77" t="inlineStr">
         <is>
           <t>IIAU</t>
         </is>
       </c>
-      <c r="TH2" s="81" t="inlineStr">
+      <c r="TH2" s="77" t="inlineStr">
         <is>
           <t>IIAUb</t>
         </is>
       </c>
-      <c r="TI2" s="81" t="inlineStr">
+      <c r="TI2" s="77" t="inlineStr">
         <is>
           <t>IVAUs</t>
         </is>
       </c>
-      <c r="TJ2" s="81" t="inlineStr">
+      <c r="TJ2" s="77" t="inlineStr">
         <is>
           <t>IXAU</t>
         </is>
       </c>
-      <c r="TK2" s="81" t="inlineStr">
+      <c r="TK2" s="77" t="inlineStr">
         <is>
           <t>VIIAUc</t>
         </is>
       </c>
-      <c r="TL2" s="81" t="inlineStr">
+      <c r="TL2" s="77" t="inlineStr">
         <is>
           <t>XAUa</t>
         </is>
       </c>
-      <c r="TM2" s="81" t="inlineStr">
+      <c r="TM2" s="77" t="inlineStr">
         <is>
           <t>XAUb</t>
         </is>
       </c>
-      <c r="TN2" s="81" t="inlineStr">
+      <c r="TN2" s="77" t="inlineStr">
         <is>
           <t>XAUc1</t>
         </is>
       </c>
-      <c r="TO2" s="81" t="inlineStr">
+      <c r="TO2" s="77" t="inlineStr">
         <is>
           <t>XAUc2b</t>
         </is>
       </c>
-      <c r="TP2" s="82" t="inlineStr">
+      <c r="TP2" s="78" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="TQ2" s="82" t="inlineStr">
+      <c r="TQ2" s="78" t="inlineStr">
         <is>
           <t>A(P2)</t>
         </is>
       </c>
-      <c r="TR2" s="82" t="inlineStr">
+      <c r="TR2" s="78" t="inlineStr">
         <is>
           <t>A(P3)</t>
         </is>
       </c>
-      <c r="TS2" s="82" t="inlineStr">
+      <c r="TS2" s="78" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="TT2" s="82" t="inlineStr">
+      <c r="TT2" s="78" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="TU2" s="82" t="inlineStr">
+      <c r="TU2" s="78" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="TV2" s="82" t="inlineStr">
+      <c r="TV2" s="78" t="inlineStr">
         <is>
           <t>Aa</t>
         </is>
       </c>
-      <c r="TW2" s="82" t="inlineStr">
+      <c r="TW2" s="78" t="inlineStr">
         <is>
           <t>Acn</t>
         </is>
       </c>
-      <c r="TX2" s="82" t="inlineStr">
+      <c r="TX2" s="78" t="inlineStr">
         <is>
           <t>Acn(P3)</t>
         </is>
       </c>
-      <c r="TY2" s="82" t="inlineStr">
+      <c r="TY2" s="78" t="inlineStr">
         <is>
           <t>Aco</t>
         </is>
       </c>
-      <c r="TZ2" s="82" t="inlineStr">
+      <c r="TZ2" s="78" t="inlineStr">
         <is>
           <t>Acu</t>
         </is>
       </c>
-      <c r="UA2" s="82" t="inlineStr">
+      <c r="UA2" s="78" t="inlineStr">
         <is>
           <t>Ae</t>
         </is>
       </c>
-      <c r="UB2" s="82" t="inlineStr">
+      <c r="UB2" s="78" t="inlineStr">
         <is>
           <t>Ae2</t>
         </is>
       </c>
-      <c r="UC2" s="82" t="inlineStr">
+      <c r="UC2" s="78" t="inlineStr">
         <is>
           <t>Ag1</t>
         </is>
       </c>
-      <c r="UD2" s="82" t="inlineStr">
+      <c r="UD2" s="78" t="inlineStr">
         <is>
           <t>Ah</t>
         </is>
       </c>
-      <c r="UE2" s="82" t="inlineStr">
+      <c r="UE2" s="78" t="inlineStr">
         <is>
           <t>Ai</t>
         </is>
       </c>
-      <c r="UF2" s="82" t="inlineStr">
+      <c r="UF2" s="78" t="inlineStr">
         <is>
           <t>Ak</t>
         </is>
       </c>
-      <c r="UG2" s="82" t="inlineStr">
+      <c r="UG2" s="78" t="inlineStr">
         <is>
           <t>An</t>
         </is>
       </c>
-      <c r="UH2" s="82" t="inlineStr">
+      <c r="UH2" s="78" t="inlineStr">
         <is>
           <t>Ap</t>
         </is>
       </c>
-      <c r="UI2" s="82" t="inlineStr">
+      <c r="UI2" s="78" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="UJ2" s="82" t="inlineStr">
+      <c r="UJ2" s="78" t="inlineStr">
         <is>
           <t>Ar</t>
         </is>
       </c>
-      <c r="UK2" s="82" t="inlineStr">
+      <c r="UK2" s="78" t="inlineStr">
         <is>
           <t>As</t>
         </is>
       </c>
-      <c r="UL2" s="82" t="inlineStr">
+      <c r="UL2" s="78" t="inlineStr">
         <is>
           <t>Atc</t>
         </is>
       </c>
-      <c r="UM2" s="82" t="inlineStr">
+      <c r="UM2" s="78" t="inlineStr">
         <is>
           <t>Atc</t>
         </is>
       </c>
-      <c r="UN2" s="82" t="inlineStr">
+      <c r="UN2" s="78" t="inlineStr">
         <is>
           <t>Ay</t>
         </is>
       </c>
-      <c r="UO2" s="82" t="inlineStr">
+      <c r="UO2" s="78" t="inlineStr">
         <is>
           <t>Azh</t>
         </is>
       </c>
-      <c r="UP2" s="83" t="inlineStr">
+      <c r="UP2" s="79" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="UQ2" s="83" t="inlineStr">
+      <c r="UQ2" s="79" t="inlineStr">
         <is>
           <t>Na</t>
         </is>
       </c>
-      <c r="UR2" s="83" t="inlineStr">
+      <c r="UR2" s="79" t="inlineStr">
         <is>
           <t>N(i)</t>
         </is>
       </c>
-      <c r="US2" s="83" t="inlineStr">
+      <c r="US2" s="79" t="inlineStr">
         <is>
           <t>N*t</t>
         </is>
       </c>
-      <c r="UT2" s="83" t="inlineStr">
+      <c r="UT2" s="79" t="inlineStr">
         <is>
           <t>Nc</t>
         </is>
       </c>
-      <c r="UU2" s="83" t="inlineStr">
+      <c r="UU2" s="79" t="inlineStr">
         <is>
           <t>Nco</t>
         </is>
       </c>
-      <c r="UV2" s="83" t="inlineStr">
+      <c r="UV2" s="79" t="inlineStr">
         <is>
           <t>Ncg</t>
         </is>
       </c>
-      <c r="UW2" s="83" t="inlineStr">
+      <c r="UW2" s="79" t="inlineStr">
         <is>
           <t>Nc1</t>
         </is>
       </c>
-      <c r="UX2" s="83" t="inlineStr">
+      <c r="UX2" s="79" t="inlineStr">
         <is>
           <t>Nel</t>
         </is>
       </c>
-      <c r="UY2" s="83" t="inlineStr">
+      <c r="UY2" s="79" t="inlineStr">
         <is>
           <t>Nenr</t>
         </is>
       </c>
-      <c r="UZ2" s="83" t="inlineStr">
+      <c r="UZ2" s="79" t="inlineStr">
         <is>
           <t>Nepr</t>
         </is>
       </c>
-      <c r="VA2" s="83" t="inlineStr">
+      <c r="VA2" s="79" t="inlineStr">
         <is>
           <t>Ner</t>
         </is>
       </c>
-      <c r="VB2" s="83" t="inlineStr">
+      <c r="VB2" s="79" t="inlineStr">
         <is>
           <t>Ne</t>
         </is>
       </c>
-      <c r="VC2" s="83" t="inlineStr">
+      <c r="VC2" s="79" t="inlineStr">
         <is>
           <t>Nj</t>
         </is>
       </c>
-      <c r="VD2" s="83" t="inlineStr">
+      <c r="VD2" s="79" t="inlineStr">
         <is>
           <t>Nf</t>
         </is>
       </c>
-      <c r="VE2" s="83" t="inlineStr">
+      <c r="VE2" s="79" t="inlineStr">
         <is>
           <t>NF</t>
         </is>
       </c>
-      <c r="VF2" s="83" t="inlineStr">
+      <c r="VF2" s="79" t="inlineStr">
         <is>
           <t>Ni</t>
         </is>
       </c>
-      <c r="VG2" s="83" t="inlineStr">
+      <c r="VG2" s="79" t="inlineStr">
         <is>
           <t>Nn</t>
         </is>
       </c>
-      <c r="VH2" s="83" t="inlineStr">
+      <c r="VH2" s="79" t="inlineStr">
         <is>
           <t>Nl</t>
         </is>
       </c>
-      <c r="VI2" s="83" t="inlineStr">
+      <c r="VI2" s="79" t="inlineStr">
         <is>
           <t>Nls</t>
         </is>
       </c>
-      <c r="VJ2" s="83" t="inlineStr">
+      <c r="VJ2" s="79" t="inlineStr">
         <is>
           <t>NLL</t>
         </is>
       </c>
-      <c r="VK2" s="83" t="inlineStr">
+      <c r="VK2" s="79" t="inlineStr">
         <is>
           <t>Ncb</t>
         </is>
       </c>
-      <c r="VL2" s="83" t="inlineStr">
+      <c r="VL2" s="79" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
-      <c r="VM2" s="83" t="inlineStr">
+      <c r="VM2" s="79" t="inlineStr">
         <is>
           <t>NMR</t>
         </is>
       </c>
-      <c r="VN2" s="83" t="inlineStr">
+      <c r="VN2" s="79" t="inlineStr">
         <is>
           <t>Np</t>
         </is>
       </c>
-      <c r="VO2" s="83" t="inlineStr">
+      <c r="VO2" s="79" t="inlineStr">
         <is>
           <t>Npi</t>
         </is>
       </c>
-      <c r="VP2" s="83" t="inlineStr">
+      <c r="VP2" s="79" t="inlineStr">
         <is>
           <t>Npv</t>
         </is>
       </c>
-      <c r="VQ2" s="83" t="inlineStr">
+      <c r="VQ2" s="79" t="inlineStr">
         <is>
           <t>Nre</t>
         </is>
       </c>
-      <c r="VR2" s="83" t="inlineStr">
+      <c r="VR2" s="79" t="inlineStr">
         <is>
           <t>NRB</t>
         </is>
       </c>
-      <c r="VS2" s="83" t="inlineStr">
+      <c r="VS2" s="79" t="inlineStr">
         <is>
           <t>NRBl</t>
         </is>
       </c>
-      <c r="VT2" s="83" t="inlineStr">
+      <c r="VT2" s="79" t="inlineStr">
         <is>
           <t>NRBl'</t>
         </is>
       </c>
-      <c r="VU2" s="83" t="inlineStr">
+      <c r="VU2" s="79" t="inlineStr">
         <is>
           <t>Ns</t>
         </is>
       </c>
-      <c r="VV2" s="83" t="inlineStr">
+      <c r="VV2" s="79" t="inlineStr">
         <is>
           <t>Nzh</t>
         </is>
       </c>
-      <c r="VW2" s="84" t="inlineStr">
+      <c r="VW2" s="80" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="VX2" s="85" t="inlineStr">
+      <c r="VX2" s="81" t="inlineStr">
         <is>
           <t>ZnC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>0961</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B4" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E4" s="88" t="n"/>
+      <c r="F4" s="88" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B5" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E5" s="88" t="n"/>
+      <c r="F5" s="88" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B6" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E6" s="88" t="n"/>
+      <c r="F6" s="88" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B7" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E7" s="88" t="n"/>
+      <c r="F7" s="88" t="inlineStr">
+        <is>
+          <t>1863</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B8" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E8" s="88" t="n"/>
+      <c r="F8" s="88" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B9" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E9" s="88" t="n"/>
+      <c r="F9" s="88" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B10" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E10" s="88" t="n"/>
+      <c r="F10" s="88" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B11" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E11" s="88" t="n"/>
+      <c r="F11" s="88" t="inlineStr">
+        <is>
+          <t>1659</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B12" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E12" s="88" t="n"/>
+      <c r="F12" s="88" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B13" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E13" s="88" t="n"/>
+      <c r="F13" s="88" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B14" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E14" s="88" t="n"/>
+      <c r="F14" s="88" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B15" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E15" s="88" t="n"/>
+      <c r="F15" s="88" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B16" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E16" s="88" t="n"/>
+      <c r="F16" s="88" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B17" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E17" s="88" t="n"/>
+      <c r="F17" s="88" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B18" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E18" s="88" t="n"/>
+      <c r="F18" s="88" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B19" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E19" s="88" t="n"/>
+      <c r="F19" s="88" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B20" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E20" s="88" t="n"/>
+      <c r="F20" s="88" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B21" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E21" s="88" t="n"/>
+      <c r="F21" s="88" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B22" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E22" s="88" t="n"/>
+      <c r="F22" s="88" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B23" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E23" s="88" t="n"/>
+      <c r="F23" s="88" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B24" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="F24" s="88" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B25" s="88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemin de Gaillardin </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="F25" s="88" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="88" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="88" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="88" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="88" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="88" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="88" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="88" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0428</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0336</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0337</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0346</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0347</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0348</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0349</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0436</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0435</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0362</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0363</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0364</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0069</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0070</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0071</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0072</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0426</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0021</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0027</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0028</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0029</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0033</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0034</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0035</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0149</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0156</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0157</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0158</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0159</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0160</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0861</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1699</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0414</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0413</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0419</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0423</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0907</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0906</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0497</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0491</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0488</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0C</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0486</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0485</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0356</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0354</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0353</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0352</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Chemin des Carres</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0875</t>
         </is>
       </c>
     </row>

--- a/state/01078_challex.xlsx
+++ b/state/01078_challex.xlsx
@@ -8628,7 +8628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:VX101"/>
+  <dimension ref="A1:VX123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="88" min="2" max="2"/>
@@ -14223,6 +14223,600 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0967</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1544</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1542</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1668</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1667</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1638</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0687</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0688</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0689</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0719</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0735</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0721</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0720</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0680</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1543</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0722</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Rue des Coteaux de Challex</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0B</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1539</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="NI1:NP1"/>

--- a/state/01078_challex.xlsx
+++ b/state/01078_challex.xlsx
@@ -8628,7 +8628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:VX123"/>
+  <dimension ref="A1:VX266"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="88" min="2" max="2"/>
@@ -14817,6 +14817,3867 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0526</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0529</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0532</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0535</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0540</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0539</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0511</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0509</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0558</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0580</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0579</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0578</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0577</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0576</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0596</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0597</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0606</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0601</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0411</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0428</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0429</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0464</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0470</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0473</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0474</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0478</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0480</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0393</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0395</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0396</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0144</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0148</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0152</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0156</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>0157</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0160</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0162</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0165</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0169</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0170</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>0171</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0174</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0767</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>0864</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>0272</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>0269</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>0278</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>0279</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0280</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>0276</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>0274</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>0263</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>0264</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>0755</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>0254</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>0253</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>0252</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>0173</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>0172</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>0163</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>0159</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>0158</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>0149</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>0384</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>0385</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>0479</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>0481</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>0475</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>0472</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>0465</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>0427</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>0844</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>0418</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>0417</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>0416</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>0412</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>0599</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>0598</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>0414</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>0595</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>0591</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>0590</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>0589</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>0587</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>0586</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>0581</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>0582</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>0508</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>0538</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>0512</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0537</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>0905</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>0525</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>0531</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Route de Pougny</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>0524</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>0029</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>0021</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Challex</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Pre Rachet</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>0D</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="NI1:NP1"/>
